--- a/evaluation/master_scoring.xlsx
+++ b/evaluation/master_scoring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\AI_Project\evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91AAEFAA-AA88-4423-903D-6A9046C72FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8777856-6E38-4774-A053-DC3866D36CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="348">
   <si>
     <t>Response ID</t>
   </si>
@@ -116,9 +116,6 @@
   </si>
   <si>
     <t>Easy</t>
-  </si>
-  <si>
-    <t>Solve for x: 3x + 12 = 30. Show each step of your calculation clearly and state the final numerical value of x.</t>
   </si>
   <si>
     <t>[FINAL ANSWER]
@@ -160,10 +157,13 @@
     <t>Completed</t>
   </si>
   <si>
-    <t>Pending</t>
+    <t>Verified</t>
   </si>
   <si>
     <t>data/responses/Q01_PHI.json</t>
+  </si>
+  <si>
+    <t>Verified correct answer x = 6. Complete step-by-step arithmetic shown without errors.</t>
   </si>
   <si>
     <t>Q01_DSR1</t>
@@ -206,6 +206,9 @@
   </si>
   <si>
     <t>data/responses/Q01_DSR1.json</t>
+  </si>
+  <si>
+    <t>Verified correct answer x = 6. Concise algebraic steps and clear boxed final answer.</t>
   </si>
   <si>
     <t>Q01_QWEN</t>
@@ -267,13 +270,13 @@
     <t>data/responses/Q01_QWEN.json</t>
   </si>
   <si>
+    <t>Verified correct answer x = 6. Thorough algebraic derivation and double-check verification.</t>
+  </si>
+  <si>
     <t>Q02_PHI</t>
   </si>
   <si>
     <t>Q02</t>
-  </si>
-  <si>
-    <t>A store offers a 20% discount on an item originally priced at $80. What is the final sale price? Show your work.</t>
   </si>
   <si>
     <t>[FINAL ANSWER]
@@ -305,6 +308,9 @@
     <t>data/responses/Q02_PHI.json</t>
   </si>
   <si>
+    <t>Verified correct sale price $64. Both 20% subtraction and 80% multiplication demonstrated.</t>
+  </si>
+  <si>
     <t>Q02_DSR1</t>
   </si>
   <si>
@@ -333,10 +339,13 @@
     <t>data/responses/Q02_DSR1.json</t>
   </si>
   <si>
+    <t>Verified correct final sale price $64. Clear discount computation and verified arithmetic.</t>
+  </si>
+  <si>
     <t>Q02_QWEN</t>
   </si>
   <si>
-    <t>&lt;think&gt;
+    <t xml:space="preserve">&lt;think&gt;
 Okay, let's see. The problem is about finding the final sale price of an item after a 20% discount. The original price is $80. Hmm, discounts can sometimes be tricky, but I think I can figure this out step by step.
 First, I need to remember how discounts work. A 20% discount means that the customer pays 80% of the original price, right? Because if you take away 20%, you're left with 100% - 20% = 80%. So instead of calculating the discount amount and subtracting it from the original price, maybe I can just calculate 80% of $80. Let me confirm that.
 Alternatively, I could calculate the discount amount first. Let me try both methods to check if they give the same result. That way, I can be sure I'm not making a mistake.
@@ -350,7 +359,8 @@
 I think all methods are converging to $64. Let me just check if there's any chance I made a calculation error. For example, if I thought 20% was 0.2, which it is, and 0.2 times 80 is 16. Yes. Then 80 minus 16 is 64. Alternatively, if I thought 20% was 0.2, and multiplied by 80, getting 16. So, no, that seems correct.
 Another way to think about percentages: 10% of 80 is 8, so 20% is double that, which is 16. Therefore, subtracting 16 from 80 gives 64. Yep, that works too.
 I think I've verified this multiple times using different methods: decimal multiplication, fraction conversion, proportion, and breaking down percentages into smaller parts. All of them lead to the same answer. Therefore, I can be confident that the final sale price after
-&lt;/think&gt;</t>
+&lt;/think&gt;
+</t>
   </si>
   <si>
     <t>2026-09-16 11:39:17</t>
@@ -359,7 +369,7 @@
     <t>data/responses/Q02_QWEN.json</t>
   </si>
   <si>
-    <t>Reached max tokens limit (num_predict=1024)</t>
+    <t>Generation truncated at 1024 token limit during extensive discount deliberation. Missing final sale price.</t>
   </si>
   <si>
     <t>Q03_PHI</t>
@@ -369,9 +379,6 @@
   </si>
   <si>
     <t>Medium</t>
-  </si>
-  <si>
-    <t>Calculate the total number of trailing zeroes in 100! (100 factorial). Explain the mathematical reasoning behind your method.</t>
   </si>
   <si>
     <t>[FINAL ANSWER]
@@ -405,10 +412,13 @@
     <t>data/responses/Q03_PHI.json</t>
   </si>
   <si>
+    <t>Verified correct answer 24 trailing zeroes. Full Legendre formula derivation for prime factor 5.</t>
+  </si>
+  <si>
     <t>Q03_DSR1</t>
   </si>
   <si>
-    <t>&lt;think&gt;
+    <t xml:space="preserve">&lt;think&gt;
 Okay, so I need to figure out how many trailing zeros are in 100 factorial, which is written as 100!. Hmm, I remember that trailing zeros are the zeros at the end of a number, right? Like, for example, 100! is a huge number, and it ends with several zeros. But how do I calculate exactly how many?
 I think it has something to do with how many times the number 10 is a factor in 100!. Because every time 10 is a factor, it adds a zero at the end. So, if I can find how many times 10 is a factor in 100!, that should give me the number of trailing zeros. But wait, 10 is 2 multiplied by 5, so maybe I need to find how many pairs of 2s and 5s are in the prime factors of 100!.
 But hold on, in any factorial, there are usually more 2s than 5s. So, the number of 5s will determine the number of trailing zeros. That makes sense because 2s are more common. So, I just need to count how many times 5 is a factor in the numbers from 1 to 100.
@@ -421,7 +431,8 @@
 Therefore, applying the same logic to 100!, it should have 24 trailing zeros. So, I think I can confidently say that the number of trailing zeros in 100! is 24.
 **Final Answer**
 The total number of trailing zeroes in 100! is \
-&lt;/think&gt;</t>
+&lt;/think&gt;
+</t>
   </si>
   <si>
     <t>2026-09-16 11:45:34</t>
@@ -430,10 +441,13 @@
     <t>data/responses/Q03_DSR1.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit while calculating factorial powers. Missing final answer.</t>
+  </si>
+  <si>
     <t>Q03_QWEN</t>
   </si>
   <si>
-    <t>&lt;think&gt;
+    <t xml:space="preserve">&lt;think&gt;
 Okay, so I need to figure out how many trailing zeros are in 100 factorial, which is 100! Let me think about how to approach this. I remember that trailing zeros are created when a number is multiplied by 10, right? And since 10 is 2 times 5, each pair of 2 and 5 in the prime factors of 100! will contribute to a trailing zero. 
 But wait, there are usually more 2s than 5s in the prime factors of a factorial. So the number of trailing zeros should depend on the number of 5s, because 5s are the limiting factor here. That makes sense because every even number contributes at least one 2, so there will be plenty of 2s to pair with the 5s. Therefore, I just need to count how many times 5 is a factor in the numbers from 1 to 100. 
 But how exactly do I do that? Let me recall. I think the method involves dividing the number by 5, then by 25, 125, etc., until the division results in zero, and then adding up all those quotients. Let me try to remember why that works. 
@@ -451,7 +465,8 @@
 10 / 5 = 2, 10 / 25 = 0. Total is 2. And 10! is 3628800, which has two trailing zeros. Correct. 
 So going back to 100! The calculation is 100 / 5 = 20, 100 / 25 = 4, 100 / 125 = 0. So total is 20 + 4 = 24. Therefore, 24 trailing zeros. 
 But let me think again why this method works. Essentially, every multiple of 5 contributes at least one 5, but multiples of higher powers of 5 contribute more. So by dividing by 5, 25, 125, etc., we account for all the 5s in the factorial. Since 2s are more plentiful, we don't
-&lt;/think&gt;</t>
+&lt;/think&gt;
+</t>
   </si>
   <si>
     <t>2026-09-16 11:40:27</t>
@@ -460,13 +475,13 @@
     <t>data/responses/Q03_QWEN.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during prime power counting. Missing final answer.</t>
+  </si>
+  <si>
     <t>Q04_PHI</t>
   </si>
   <si>
     <t>Q04</t>
-  </si>
-  <si>
-    <t>Find the next two numbers in the sequence: 2, 6, 12, 20, 30, ... Explain the underlying rule governing the pattern.</t>
   </si>
   <si>
     <t>&lt;think&gt;
@@ -506,6 +521,9 @@
   </si>
   <si>
     <t>data/responses/Q04_PHI.json</t>
+  </si>
+  <si>
+    <t>Generation truncated at 1024 token limit during &lt;think&gt; step. Partial sequence deduction; missing final answer.</t>
   </si>
   <si>
     <t>Q04_DSR1</t>
@@ -568,10 +586,13 @@
     <t>data/responses/Q04_DSR1.json</t>
   </si>
   <si>
+    <t>Verified correct numbers 42 and 56. Identified second differences pattern and n*(n+1) rule.</t>
+  </si>
+  <si>
     <t>Q04_QWEN</t>
   </si>
   <si>
-    <t>&lt;think&gt;
+    <t xml:space="preserve">&lt;think&gt;
 Okay, let's see. I need to find the next two numbers in the sequence: 2, 6, 12, 20, 30, ... and explain the rule. Hmm, let me start by looking at the differences between the numbers. 
 First, let me write down the terms with their positions to see if that helps. Let's say the first term is term 1, second term is term 2, etc.
 Term 1: 2  
@@ -615,7 +636,8 @@
 = n² + n - (n² - n)  
 = n² + n - n² + n  
 =
-&lt;/think&gt;</t>
+&lt;/think&gt;
+</t>
   </si>
   <si>
     <t>2026-09-16 11:41:41</t>
@@ -624,6 +646,9 @@
     <t>data/responses/Q04_QWEN.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during sequence pattern hypothesis testing. Missing next terms.</t>
+  </si>
+  <si>
     <t>Q05_PHI</t>
   </si>
   <si>
@@ -631,9 +656,6 @@
   </si>
   <si>
     <t>Hard</t>
-  </si>
-  <si>
-    <t>Three fair standard six-sided dice are rolled simultaneously. What is the exact probability that the sum of the numbers rolled is equal to 10? Express your answer as a simplified fraction and explain each step.</t>
   </si>
   <si>
     <t>&lt;think&gt;
@@ -658,10 +680,13 @@
     <t>data/responses/Q05_PHI.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during combinatorial expansion. Missing final probability fraction.</t>
+  </si>
+  <si>
     <t>Q05_DSR1</t>
   </si>
   <si>
-    <t>&lt;think&gt;
+    <t xml:space="preserve">&lt;think&gt;
 Okay, so I have this problem where I need to find the probability that the sum of three fair six-sided dice is equal to 10. Hmm, let me think about how to approach this. I remember that when dealing with probabilities involving dice, it's often useful to figure out the number of favorable outcomes divided by the total number of possible outcomes. 
 First, let me recall that each die has 6 faces, so when rolling three dice, the total number of possible outcomes is 6 multiplied by itself three times, which is 6^3. Let me calculate that: 6*6 is 36, and 36*6 is 216. So, there are 216 possible outcomes when rolling three dice. Got that down.
 Now, the tricky part is figuring out how many of these outcomes result in a sum of 10. I think this is a combinatorics problem where I need to find the number of integer solutions to the equation a + b + c = 10, where each of a, b, and c is at least 1 and at most 6. Because each die can only show a number from 1 to 6, inclusive.
@@ -674,7 +699,8 @@
 Wait, hold on. Let me verify that. So, the initial number of solutions is 36. Then, for each die, if it exceeds 5, we subtract 3. Since there are three dice, that's 3*3=9. So 36 - 9 = 27. That seems right.
 But just to make sure, maybe I can list all the possible combinations that sum to 10 with three dice. Let me see.
 Alternatively, maybe I can think of it as
-&lt;/think&gt;</t>
+&lt;/think&gt;
+</t>
   </si>
   <si>
     <t>2026-09-16 11:47:50</t>
@@ -683,10 +709,13 @@
     <t>data/responses/Q05_DSR1.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during dice sum partitions. Incomplete calculation.</t>
+  </si>
+  <si>
     <t>Q05_QWEN</t>
   </si>
   <si>
-    <t>&lt;think&gt;
+    <t xml:space="preserve">&lt;think&gt;
 Okay, so I need to find the probability that when rolling three standard six-sided dice, the sum is exactly 10. Let me think about how to approach this. 
 First, I remember that when dealing with probabilities involving dice, it's often helpful to figure out the total number of possible outcomes and then determine how many of those outcomes result in the desired sum. Since each die has 6 sides, and we're rolling three dice, the total number of possible outcomes should be 6 multiplied by itself three times. Let me write that down:
 Total outcomes = 6 × 6 × 6 = 216.
@@ -709,7 +738,8 @@
 |A ∪ B ∪ C| = |A| + |B| + |C| - |A ∩ B| - |A ∩ C| - |B ∩ C| + |A ∩ B ∩ C|.
 First, compute |A|. If a' ≥ 6, let me set a'' = a' - 6 ≥ 0. Then the equation becomes a'' + 6 + b' + c' = 7 ⇒ a'' + b' + c' = 1. The number of non-negative solutions is C(1 + 3 - 1, 3 - 1) = C(3, 2) = 3. Similarly, |B| = |C| = 3. So total for |A| + |B| + |C| = 3*3 = 9.
 Next, compute |A ∩ B|. This is the number of solutions where
-&lt;/think&gt;</t>
+&lt;/think&gt;
+</t>
   </si>
   <si>
     <t>2026-09-16 11:42:45</t>
@@ -718,6 +748,9 @@
     <t>data/responses/Q05_QWEN.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during generating function formulation. Missing final probability.</t>
+  </si>
+  <si>
     <t>Q06_PHI</t>
   </si>
   <si>
@@ -725,9 +758,6 @@
   </si>
   <si>
     <t>Logical reasoning</t>
-  </si>
-  <si>
-    <t>A farmer has 17 sheep, and all but 9 die. How many live sheep does the farmer have left? State your answer and briefly explain the logic.</t>
   </si>
   <si>
     <t>[FINAL ANSWER]
@@ -747,6 +777,9 @@
   </si>
   <si>
     <t>data/responses/Q06_PHI.json</t>
+  </si>
+  <si>
+    <t>Verified correct answer 9 live sheep. Clean semantic deduction avoiding subtraction trap.</t>
   </si>
   <si>
     <t>Q06_DSR1</t>
@@ -782,6 +815,9 @@
     <t>data/responses/Q06_DSR1.json</t>
   </si>
   <si>
+    <t>Verified correct answer 9 live sheep. Accurate explanation of 'all but 9' linguistic phrasing.</t>
+  </si>
+  <si>
     <t>Q06_QWEN</t>
   </si>
   <si>
@@ -808,13 +844,13 @@
     <t>data/responses/Q06_QWEN.json</t>
   </si>
   <si>
+    <t>Verified correct answer 9 live sheep. Sound semantic disambiguation and explicit conclusion.</t>
+  </si>
+  <si>
     <t>Q07_PHI</t>
   </si>
   <si>
     <t>Q07</t>
-  </si>
-  <si>
-    <t>All roses are flowers. Some flowers fade quickly. Does it strictly follow that some roses fade quickly? Answer with 'Yes' or 'No' and provide a formal logical justification.</t>
   </si>
   <si>
     <t>[FINAL ANSWER]
@@ -850,6 +886,9 @@
     <t>data/responses/Q07_PHI.json</t>
   </si>
   <si>
+    <t>Verified correct answer 'No'. Sound logical justification based on undistributed middle set relation.</t>
+  </si>
+  <si>
     <t>Q07_DSR1</t>
   </si>
   <si>
@@ -880,6 +919,9 @@
     <t>data/responses/Q07_DSR1.json</t>
   </si>
   <si>
+    <t>Incorrect final answer 'Yes' (expected 'No'). Committed formal fallacy of the undistributed middle.</t>
+  </si>
+  <si>
     <t>Q07_QWEN</t>
   </si>
   <si>
@@ -909,13 +951,13 @@
     <t>data/responses/Q07_QWEN.json</t>
   </si>
   <si>
+    <t>Verified correct answer 'No'. Rigorous formal logic predicate justification disproving necessity.</t>
+  </si>
+  <si>
     <t>Q08_PHI</t>
   </si>
   <si>
     <t>Q08</t>
-  </si>
-  <si>
-    <t>Alice, Bob, and Charlie are sitting in a row. Alice is not on the far right. Bob is sitting to the immediate right of Alice. Who is sitting on the far left? Deduce the exact left-to-right seating arrangement step by step.</t>
   </si>
   <si>
     <t>&lt;think&gt;
@@ -942,6 +984,9 @@
   </si>
   <si>
     <t>data/responses/Q08_PHI.json</t>
+  </si>
+  <si>
+    <t>Generation truncated at 1024 token limit during seating permutation search. Missing final arrangement.</t>
   </si>
   <si>
     <t>Q08_DSR1</t>
@@ -984,10 +1029,13 @@
     <t>data/responses/Q08_DSR1.json</t>
   </si>
   <si>
+    <t>Verified correct deduction: Alice on far left (order: Alice, Bob, Charlie). Step-by-step constraint elimination.</t>
+  </si>
+  <si>
     <t>Q08_QWEN</t>
   </si>
   <si>
-    <t>&lt;think&gt;
+    <t xml:space="preserve">&lt;think&gt;
 Okay, let's try to figure out this seating arrangement problem. So, we have Alice, Bob, and Charlie sitting in a row. The question says Alice is not on the far right. Also, Bob is sitting to the immediate right of Alice. We need to determine who is sitting on the far left. Let me break this down step by step.
 First, let me recall that there are three people: Alice, Bob, and Charlie. They are sitting in a row, which means there are three seats in a straight line. The positions can be considered as left to right: Position 1 (far left), Position 2 (middle), and Position 3 (far right).
 The first condition is that Alice is not on the far right. So Alice cannot be in Position 3. That leaves Alice possibly in Position 1 or Position 2.
@@ -1006,7 +1054,8 @@
 If there are three seats, and Alice cannot be on the far right, so she can be in seat 1 or 2. If she is in seat 1, Bob is in seat 2, so Charlie is in seat 3. If she is in seat 2, Bob is in seat 3, so Charlie is in seat 1. Both are valid. Therefore, there are two possible arrangements. However, the problem says "Deduce the exact left-to-right seating arrangement." Maybe there's more constraints?
 Wait, maybe I need to check if there are any other constraints. The problem says "Alice, Bob, and Charlie are sitting in a row." So all three are seated, no one is missing. The problem doesn't mention anything else. Therefore, both arrangements are possible. But the question is asking "Who is sitting on the far left?" So maybe there's a unique answer? Maybe I need to check if there's something wrong with my reasoning.
 Alternatively, maybe the problem assumes that there are three seats, so positions 1, 2,
-&lt;/think&gt;</t>
+&lt;/think&gt;
+</t>
   </si>
   <si>
     <t>2026-09-16 11:32:29</t>
@@ -1015,13 +1064,13 @@
     <t>data/responses/Q08_QWEN.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during exhaustive linear permutation analysis. Missing answer.</t>
+  </si>
+  <si>
     <t>Q09_PHI</t>
   </si>
   <si>
     <t>Q09</t>
-  </si>
-  <si>
-    <t>You have a 3-liter jug and a 5-liter jug, and an unlimited supply of water. How can you measure out exactly 4 liters using only these two jugs without any measuring scales? Detail every pour step.</t>
   </si>
   <si>
     <t>&lt;think&gt;
@@ -1061,6 +1110,9 @@
   </si>
   <si>
     <t>data/responses/Q09_PHI.json</t>
+  </si>
+  <si>
+    <t>Generation truncated at 1024 token limit during jug state search. Incomplete pour sequence.</t>
   </si>
   <si>
     <t>Q09_DSR1</t>
@@ -1115,10 +1167,13 @@
     <t>data/responses/Q09_DSR1.json</t>
   </si>
   <si>
+    <t>Verified correct 4-liter measurement in 5L jug. Flawless 6-step state transition sequence.</t>
+  </si>
+  <si>
     <t>Q09_QWEN</t>
   </si>
   <si>
-    <t>&lt;think&gt;
+    <t xml:space="preserve">&lt;think&gt;
 Okay, so I need to figure out how to measure exactly 4 liters using a 3-liter jug and a 5-liter jug. Let me think about this step by step. 
 First, I know that these kinds of problems usually involve filling up one jug, pouring into the other, and keeping track of the amounts. Since the jugs are 3 and 5 liters, their capacities are different, so I need to find a way to get to 4 liters. Let me recall if there's a standard method for these kinds of problems. 
 I remember that the key is to use the fact that the greatest common divisor (GCD) of 3 and 5 is 1, which means we can measure any integer amount up to the sum of the capacities, which is 8 liters. Since 4 is less than 8, it should be possible. 
@@ -1149,7 +1204,8 @@
 Step 8: Pour from 3 into 5. 5 can take 5 - 1 = 4 liters, but 3 only has 3 liters. So pour all 3 liters into 5, making 5 have 1 + 3 = 4 liters. 
 So here, the 5-liter jug has 4 liters. So this is another way. So there are multiple methods. The question says to detail every pour step. Let me check which method is more straightforward. 
 The first method I thought of was filling the 5-liter first, then transferring. The second method fills the 3-liter first. Both work
-&lt;/think&gt;</t>
+&lt;/think&gt;
+</t>
   </si>
   <si>
     <t>2026-09-16 11:33:56</t>
@@ -1158,13 +1214,13 @@
     <t>data/responses/Q09_QWEN.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during state space tree exploration. Missing final pour sequence.</t>
+  </si>
+  <si>
     <t>Q10_PHI</t>
   </si>
   <si>
     <t>Q10</t>
-  </si>
-  <si>
-    <t>On an island, inhabitants are either Knights (who always tell the truth) or Knaves (who always lie). You meet two inhabitants, A and B. A says: 'At least one of us is a Knave.' Determine precisely what A is and what B is. Provide a rigorous proof by cases.</t>
   </si>
   <si>
     <t>&lt;think&gt;
@@ -1198,10 +1254,13 @@
     <t>data/responses/Q10_PHI.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during truth table case analysis. Missing final knight/knave classification.</t>
+  </si>
+  <si>
     <t>Q10_DSR1</t>
   </si>
   <si>
-    <t>&lt;think&gt;
+    <t xml:space="preserve">&lt;think&gt;
 Okay, so I have this logic puzzle here about two inhabitants, A and B, on an island where everyone is either a Knight who always tells the truth or a Knave who always lies. A says, "At least one of us is a Knave." I need to figure out whether A is a Knight or a Knave, and the same for B. Hmm, let me think through this step by step.
 First, let me recall that Knights always tell the truth, so whatever they say must be true. Knaves always lie, so whatever they say must be false. So, if A is a Knight, then A's statement must be true. If A is a Knave, then A's statement must be false.
 A says, "At least one of us is a Knave." So, let's break this down. The statement "at least one of us is a Knave" can be translated into logical terms as "A is a Knave or B is a Knave." In symbols, that would be A ∨ B, where A and B represent whether A and B are Knaves, respectively. Wait, actually, hold on. If A is a Knight, then A tells the truth, so "at least one of us is a Knave" must be true. If A is a Knave, then the statement is false, so "at least one of us is a Knave" is false, meaning neither A nor B is a Knave, so both would be Knights.
@@ -1227,7 +1286,8 @@
    - A's statement: "At least one of us is a Knave." This is true because B is a Knave. So, consistent.
 3. A is a Knave, B is a Knight.
    - A's statement: "At least one of us is a Knave." Since A is a Knave, the
-&lt;/think&gt;</t>
+&lt;/think&gt;
+</t>
   </si>
   <si>
     <t>2026-09-16 11:27:36</t>
@@ -1236,10 +1296,13 @@
     <t>data/responses/Q10_DSR1.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during proof by cases. Incomplete knight/knave deduction.</t>
+  </si>
+  <si>
     <t>Q10_QWEN</t>
   </si>
   <si>
-    <t>&lt;think&gt;
+    <t xml:space="preserve">&lt;think&gt;
 Okay, so I need to figure out whether A and B are Knights or Knaves based on A's statement. Let me start by recalling that Knights always tell the truth, and Knaves always lie. The statement A makes is: "At least one of us is a Knave." 
 First, let me consider the possibilities. There are two inhabitants, A and B. Each can be either a Knight or a Knave. So there are four possible combinations:
 1. A is a Knight and B is a Knight.
@@ -1266,7 +1329,8 @@
 - Case 4: Contradiction.
 Therefore, the only possible case is Case 2: A is a Knight and B is a Knave.
 Wait, but let me check again. In Case 3, if A is a Knave and B is a Knight, then A's statement is "At least one of us is a Knave." Since A is lying, the truth is that "At least one of us is a Knave" is false, which would mean that both are Knights. But in reality, A is a Knave and B is a Knight, so there is at least one Knave (A). Therefore, the statement "At least one of us
-&lt;/think&gt;</t>
+&lt;/think&gt;
+</t>
   </si>
   <si>
     <t>2026-09-16 11:35:11</t>
@@ -1275,6 +1339,9 @@
     <t>data/responses/Q10_QWEN.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during logical contradiction derivation. Incomplete proof.</t>
+  </si>
+  <si>
     <t>Q11_PHI</t>
   </si>
   <si>
@@ -1282,9 +1349,6 @@
   </si>
   <si>
     <t>Programming reasoning</t>
-  </si>
-  <si>
-    <t>Write a clean Python function `is_palindrome(s: str) -&gt; bool` that checks if a string is a palindrome, ignoring non-alphanumeric characters and case. Provide a brief trace of why it works.</t>
   </si>
   <si>
     <t>[FINAL ANSWER]
@@ -1334,10 +1398,13 @@
     <t>data/responses/Q11_PHI.json</t>
   </si>
   <si>
+    <t>Verified correct implementation of is_palindrome. Correctly uses isalnum(), lower(), and reverse slice.</t>
+  </si>
+  <si>
     <t>Q11_DSR1</t>
   </si>
   <si>
-    <t>&lt;think&gt;
+    <t xml:space="preserve">&lt;think&gt;
 Okay, I need to write a Python function called is_palindrome that checks if a string is a palindrome, but ignoring non-alphanumeric characters and case. Hmm, let's think about how to approach this.
 First, what's a palindrome? It's a string that reads the same backward as forward. But I need to ignore non-alphanumeric characters and case. So, for example, "A man, a plan, a canal: Panama" should return True because when you remove the non-alphanumeric characters and make everything lowercase, it's a palindrome.
 So, the steps I need to take are:
@@ -1404,7 +1471,8 @@
 Wait, that's 10 characters. So, the filtered string is "noxni xion"? Wait, no, it's "noxniNixion"? Wait, no, let's process each character:
 1. N -&gt; n
 2. o -&gt; o
-&lt;/think&gt;</t>
+&lt;/think&gt;
+</t>
   </si>
   <si>
     <t>2026-09-16 12:23:45</t>
@@ -1413,10 +1481,13 @@
     <t>data/responses/Q11_DSR1.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during palindrome trace. Function implementation cut off.</t>
+  </si>
+  <si>
     <t>Q11_QWEN</t>
   </si>
   <si>
-    <t>&lt;think&gt;
+    <t xml:space="preserve">&lt;think&gt;
 Okay, I need to write a Python function called is_palindrome that checks if a string is a palindrome, ignoring non-alphanumeric characters and case. Let me think about how to approach this.
 First, what's a palindrome? It's a string that reads the same forwards and backwards. But the problem says to ignore non-alphanumeric characters and case. So, I need to process the string to remove any characters that aren't letters or numbers, and then convert everything to the same case, like lowercase.
 So the steps I need to take are:
@@ -1452,7 +1523,8 @@
 So the function works by preprocessing the input string to remove non-alphanumeric characters and normalize case, then checking for palindrome properties by comparing the processed string with its reverse.
 I think that's correct. Let me check for possible errors.
 Wait, what about Unicode characters? For example, characters that are alphanumeric but not in the ASCII range. The isalnum() method in Python handles Unicode characters. For example, 'é' is considered alphanumeric in Python 3. So, if the input has such characters, they would be included. But
-&lt;/think&gt;</t>
+&lt;/think&gt;
+</t>
   </si>
   <si>
     <t>2026-09-16 12:29:41</t>
@@ -1461,18 +1533,13 @@
     <t>data/responses/Q11_QWEN.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during string manipulation comparison. Missing completed function.</t>
+  </si>
+  <si>
     <t>Q12_PHI</t>
   </si>
   <si>
     <t>Q12</t>
-  </si>
-  <si>
-    <t>Trace the execution of this Python code snippet and determine the exact printed output:
-x = [1, 2, 3]
-y = x
-y.append(4)
-print(len(x), x == y)
-Explain why `len(x)` is affected.</t>
   </si>
   <si>
     <t>&lt;think&gt;
@@ -1503,6 +1570,9 @@
     <t>data/responses/Q12_PHI.json</t>
   </si>
   <si>
+    <t>Incorrect final answer '3 False' (expected '4 True'). Fundamental conceptual error regarding Python mutable list references.</t>
+  </si>
+  <si>
     <t>Q12_DSR1</t>
   </si>
   <si>
@@ -1525,6 +1595,9 @@
   </si>
   <si>
     <t>data/responses/Q12_DSR1.json</t>
+  </si>
+  <si>
+    <t>Verified correct printed output '4 True'. Thorough explanation of shared reference and in-place list mutation.</t>
   </si>
   <si>
     <t>Q12_QWEN</t>
@@ -1592,25 +1665,13 @@
     <t>data/responses/Q12_QWEN.json</t>
   </si>
   <si>
+    <t>Verified correct printed output '4 True'. Clear explanation of pointer aliasing and memory object mutation.</t>
+  </si>
+  <si>
     <t>Q13_PHI</t>
   </si>
   <si>
     <t>Q13</t>
-  </si>
-  <si>
-    <t>Identify the bug in the following binary search implementation and explain how to fix it:
-def binary_search(arr, target):
-    low = 0
-    high = len(arr)
-    while low &lt; high:
-        mid = (low + high) // 2
-        if arr[mid] == target:
-            return mid
-        elif arr[mid] &lt; target:
-            low = mid
-        else:
-            high = mid - 1
-    return -1</t>
   </si>
   <si>
     <t>&lt;think&gt;
@@ -1635,10 +1696,13 @@
     <t>data/responses/Q13_PHI.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during binary search analysis. Missing explicit code fix.</t>
+  </si>
+  <si>
     <t>Q13_DSR1</t>
   </si>
   <si>
-    <t>&lt;think&gt;
+    <t xml:space="preserve">&lt;think&gt;
 Okay, so I need to figure out what's wrong with this binary search implementation. Let me look at the code step by step.
 The function is called binary_search and takes an array 'arr' and a target value. It initializes 'low' to 0 and 'high' to the length of the array. Then it enters a while loop that continues as long as 'low' is less than 'high'.
 Inside the loop, it calculates 'mid' as the average of 'low' and 'high', using integer division. Then it checks if the element at 'mid' is equal to the target. If so, it returns 'mid'. That seems correct.
@@ -1663,7 +1727,8 @@
 Another example: target is 7.
 First mid=2, arr[2]=5 &lt;7, so low=3.
 Now low=3, high=4. mid=(3+4)//2=3. arr[3]=7, returns 3.
-&lt;/think&gt;</t>
+&lt;/think&gt;
+</t>
   </si>
   <si>
     <t>2026-09-16 12:25:52</t>
@@ -1672,10 +1737,13 @@
     <t>data/responses/Q13_DSR1.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during binary search analysis. Missing final corrected code block.</t>
+  </si>
+  <si>
     <t>Q13_QWEN</t>
   </si>
   <si>
-    <t>&lt;think&gt;
+    <t xml:space="preserve">&lt;think&gt;
 Okay, let's see. I need to find the bug in this binary search implementation. Let me start by understanding the code step by step.
 The function is called binary_search, taking an array and a target. The initial low is 0, high is len(arr). Then there's a loop while low &lt; high. Inside the loop, mid is calculated as (low + high) divided by 2, using integer division. 
 If the element at mid is equal to the target, return mid. If it's less than the target, set low to mid. Otherwise, set high to mid - 1. If the loop ends, return -1.
@@ -1689,7 +1757,8 @@
 Wait, but what if the array has length 1? Let's say arr is [5], target is 5. Then high is len(arr) = 1. So loop runs while 0 &lt; 1. mid is (0+1)/2 = 0.5 → 0. arr[0] is 5, return 0. Correct.
 Hmm. So maybe the initial high being len(arr) is okay? But wait, in some implementations, high is set to len(arr)-1. So why is this code using len(arr) instead?
 Wait, perhaps there's another issue. Let me think about when the array is not sorted. But the problem says it's a binary search, so perhaps the array is
-&lt;/think&gt;</t>
+&lt;/think&gt;
+</t>
   </si>
   <si>
     <t>2026-09-16 12:32:33</t>
@@ -1698,13 +1767,13 @@
     <t>data/responses/Q13_QWEN.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during binary search edge condition tracing. Missing bug fix.</t>
+  </si>
+  <si>
     <t>Q14_PHI</t>
   </si>
   <si>
     <t>Q14</t>
-  </si>
-  <si>
-    <t>Describe Floyd's Cycle-Finding Algorithm (Tortoise and Hare) for detecting a loop in a singly linked list. Explain why the time complexity is O(N) and the auxiliary space complexity is O(1).</t>
   </si>
   <si>
     <t>&lt;think&gt;
@@ -1722,6 +1791,9 @@
   </si>
   <si>
     <t>data/responses/Q14_PHI.json</t>
+  </si>
+  <si>
+    <t>Generation truncated at 1024 token limit during cycle detection proof. Missing formal complexity conclusion.</t>
   </si>
   <si>
     <t>Q14_DSR1</t>
@@ -1760,10 +1832,13 @@
     <t>data/responses/Q14_DSR1.json</t>
   </si>
   <si>
+    <t>Verified complete explanation of Floyd's Tortoise and Hare. Accurate proofs for O(N) time and O(1) space.</t>
+  </si>
+  <si>
     <t>Q14_QWEN</t>
   </si>
   <si>
-    <t>&lt;think&gt;
+    <t xml:space="preserve">&lt;think&gt;
 Okay, so I need to explain Floyd's Cycle-Finding Algorithm, also known as the Tortoise and Hare algorithm, for detecting a loop in a singly linked list. Let me start by recalling what I know about this algorithm.
 First, the problem is to determine if a singly linked list has a cycle. A cycle means that somewhere in the list, a node points to a node that's already been visited before, creating a loop. The challenge is to detect this without using extra space, right? Because if we use a hash table to track visited nodes, that would take O(N) space, which isn't optimal.
 Floyd's algorithm uses two pointers, one moving slower than the other. The idea is that if there's a cycle, the faster pointer will eventually catch up to the slower one. Let me think about how that works.
@@ -1777,7 +1852,8 @@
 But why does the meeting happen? Let me think of the mathematical proof. Let’s assume that the list has a cycle. Let’s say the distance from the start to the cycle entrance is 'a', and the cycle length is 'l'. Let’s say the tortoise and hare start moving. The tortoise moves at speed 1, hare at speed 2. Let’s say they meet after the tortoise has traveled 'd' steps. Then the hare has traveled '2d' steps. The difference between their paths is 2d - d = d. Since they meet, this difference must be a multiple of the cycle length. So d = k*l. But how does this ensure that they meet?
 Alternatively, think about the meeting point. Let’s say the tortoise enters the cycle after 'a' steps. Then, the hare has already traveled 'a' steps as well (since hare is moving twice as fast, but maybe not? Wait, no. Wait, the hare starts at the same time as the tortoise. So when the tortoise reaches the cycle entrance, the hare has already moved twice as far. Let me think again.
 Let me consider that the tortoise and hare start at the head. Let’s say the tortoise reaches the cycle entrance after 'a' steps. At that point, the hare has moved 2a steps. Since the cycle length is 'l', the hare is now at position (2a mod l) in the cycle. Then, both continue moving. The tortoise
-&lt;/think&gt;</t>
+&lt;/think&gt;
+</t>
   </si>
   <si>
     <t>2026-09-16 12:34:20</t>
@@ -1786,13 +1862,13 @@
     <t>data/responses/Q14_QWEN.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during cycle convergence mathematical proof. Missing final text.</t>
+  </si>
+  <si>
     <t>Q15_PHI</t>
   </si>
   <si>
     <t>Q15</t>
-  </si>
-  <si>
-    <t>Propose an optimal algorithm in Python to find the Longest Increasing Subsequence (LIS) in O(N log N) time complexity using patience sorting / binary search. Provide the complete code, step-by-step invariant explanation, and complexity analysis.</t>
   </si>
   <si>
     <t>&lt;think&gt;
@@ -1835,10 +1911,13 @@
     <t>data/responses/Q15_PHI.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during patience sorting explanation. Missing complete algorithm code.</t>
+  </si>
+  <si>
     <t>Q15_DSR1</t>
   </si>
   <si>
-    <t>&lt;think&gt;
+    <t xml:space="preserve">&lt;think&gt;
 Okay, so I need to figure out how to implement the optimal algorithm for finding the Longest Increasing Subsequence (LIS) in O(N log N) time. I remember that the patience sorting method is used here, which involves some kind of binary search. Let me try to break this down step by step.
 First, I know that the LIS problem is about finding the longest subsequence of a given sequence where the elements are in increasing order. A subsequence doesn't have to be contiguous, right? So, for example, if the sequence is [10, 9, 2, 5, 3, 7, 1], the LIS would be [2,3,7], which has a length of 3.
 Now, the patience sorting approach. From what I recall, it's inspired by the card game where you sort piles by placing each card on top of the first pile that is larger than it. Each pile represents an increasing subsequence. The number of piles at the end gives the length of the LIS.
@@ -1874,7 +1953,8 @@
         tails[idx] = num
 The length of tails is the length of the LIS.
 Wait, but wait. Let me
-&lt;/think&gt;</t>
+&lt;/think&gt;
+</t>
   </si>
   <si>
     <t>2026-09-16 12:28:17</t>
@@ -1883,10 +1963,13 @@
     <t>data/responses/Q15_DSR1.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during patience sorting patience sorting trace. Incomplete implementation.</t>
+  </si>
+  <si>
     <t>Q15_QWEN</t>
   </si>
   <si>
-    <t>&lt;think&gt;
+    <t xml:space="preserve">&lt;think&gt;
 Okay, I need to figure out how to implement the Longest Increasing Subsequence (LIS) in O(N log N) time using patience sorting and binary search. Let me start by recalling what the LIS problem is. The LIS is the longest subsequence in a given sequence where the elements are in increasing order. A subsequence doesn't require elements to be consecutive, just in order.
 The standard approach for O(N log N) is using binary search with a method similar to patience sorting. I remember that the idea is to maintain a list where each element represents the smallest possible tail of an increasing subsequence of a certain length. For example, if we have a list of tails, for each number in the array, we find the first element in the tails list that is greater than or equal to the current number and replace it with the current number. This way, the tails list remains sorted, and we can use binary search to find the insertion point efficiently.
 Let me think about the steps. For each element in the array, we do a binary search on the tails list to find the position where the current element can replace an existing entry. If the current element is larger than all elements in tails, we append it. Otherwise, we replace the first element in tails that is greater than or equal to the current element. The length of the tails list at the end will be the length of the LIS.
@@ -1901,7 +1984,8 @@
 In any case, the code for the length is straightforward. Let me proceed with that first. But perhaps the user wants the actual sequence. Let me check the standard approach. For example, the patience sorting algorithm can be used to find the length, but to reconstruct the sequence, you need to track the predecessors. However, that might complicate things. Let me check the original question again. The user says "find the LIS", which could be ambiguous. However, given that the user mentions O(N log N) time, which is standard for the length, perhaps they just want the length. However, maybe they want the actual sequence. Let me check the initial problem again.
 The user says "find the Longest Increasing Subsequence (LIS)", which could mean the actual sequence. However, the standard O(N log N) algorithm for LIS gives the length. But there's a way to reconstruct the sequence with O(N) space. However, that might require additional steps. Let me think. For example, during the process, we can track the indices. But perhaps the user is okay with just the length. Let me check the initial problem again. The user says "complete code", so maybe they want the code that returns the actual sequence. However, the standard approach with patience sorting gives the length. Let me check the standard approach.
 Alternatively, perhaps the user is okay with
-&lt;/think&gt;</t>
+&lt;/think&gt;
+</t>
   </si>
   <si>
     <t>2026-09-16 12:35:54</t>
@@ -1910,6 +1994,9 @@
     <t>data/responses/Q15_QWEN.json</t>
   </si>
   <si>
+    <t>Generation truncated at 1024 token limit during patience sorting bisect code writing. Missing complete solution.</t>
+  </si>
+  <si>
     <t>Benchmarking Metrics Summary (Page 3 Calculations)</t>
   </si>
   <si>
@@ -2000,14 +2087,192 @@
     <t>Expected Key Reasoning Points</t>
   </si>
   <si>
-    <t>Note: After each benchmark is done, it has automatically free VRAM to be ready for the next benchmark run.</t>
+    <t>Solve for x: 3x + 12 = 30. Show each step of your calculation clearly and state the final numerical value of x.</t>
+  </si>
+  <si>
+    <t>x = 6</t>
+  </si>
+  <si>
+    <t>1. Subtract 12 from both sides: 3x = 18.
+2. Divide both sides by 3: x = 18 / 3 = 6.
+3. Clearly state final numerical value x = 6.</t>
+  </si>
+  <si>
+    <t>A store offers a 20% discount on an item originally priced at $80. What is the final sale price? Show your work.</t>
+  </si>
+  <si>
+    <t>$64</t>
+  </si>
+  <si>
+    <t>1. Calculate discount: 20% of $80 = 0.20 * 80 = $16 (or 80% of $80 = $64).
+2. Subtract discount from original: $80 - $16 = $64.
+3. State final sale price of $64.</t>
+  </si>
+  <si>
+    <t>Calculate the total number of trailing zeroes in 100! (100 factorial). Explain the mathematical reasoning behind your method.</t>
+  </si>
+  <si>
+    <t>24 trailing zeroes</t>
+  </si>
+  <si>
+    <t>1. Trailing zeroes are produced by 10 = 2 * 5. Factors of 2 are abundant, count factors of 5.
+2. Apply Legendre's formula: floor(100/5) + floor(100/25) = 20 + 4 = 24.
+3. Powers of 5 &gt; 100 contribute 0, giving exactly 24.</t>
+  </si>
+  <si>
+    <t>Find the next two numbers in the sequence: 2, 6, 12, 20, 30, ... Explain the underlying rule governing the pattern.</t>
+  </si>
+  <si>
+    <t>42 and 56</t>
+  </si>
+  <si>
+    <t>1. Constant second differences: +4, +6, +8, +10; next differences are +12 (30 + 12 = 42) and +14 (42 + 14 = 56).
+2. Or general term n*(n+1) for n=6 (42) and n=7 (56).
+3. State both numbers: 42 and 56.</t>
+  </si>
+  <si>
+    <t>Three fair standard six-sided dice are rolled simultaneously. What is the exact probability that the sum of the numbers rolled is equal to 10? Express your answer as a simplified fraction and explain each step.</t>
+  </si>
+  <si>
+    <t>1/8 (or 27/216)</t>
+  </si>
+  <si>
+    <t>1. Total outcomes = 6^3 = 216.
+2. Favorable partitions summing to 10 from 3 dice (1 to 6) total 27 outcomes.
+3. Simplified fraction = 27 / 216 = 1/8.</t>
+  </si>
+  <si>
+    <t>A farmer has 17 sheep, and all but 9 die. How many live sheep does the farmer have left? State your answer and briefly explain the logic.</t>
+  </si>
+  <si>
+    <t>9 live sheep</t>
+  </si>
+  <si>
+    <t>1. Semantic meaning of 'all but 9 die' means exactly 9 live sheep survive.
+2. Avoid subtracting 9 from 17 (17 - 9 = 8).
+3. Conclude decisively that 9 live sheep remain.</t>
+  </si>
+  <si>
+    <t>All roses are flowers. Some flowers fade quickly. Does it strictly follow that some roses fade quickly? Answer with 'Yes' or 'No' and provide a formal logical justification.</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>1. Direct answer: No.
+2. Formal set logic: Some flowers fade quickly does not entail that the specific subset of flowers that are roses fade quickly.
+3. Fallacy of the undistributed middle.</t>
+  </si>
+  <si>
+    <t>Alice, Bob, and Charlie are sitting in a row. Alice is not on the far right. Bob is sitting to the immediate right of Alice. Who is sitting on the far left? Deduce the exact left-to-right seating arrangement step by step.</t>
+  </si>
+  <si>
+    <t>Alice is on the far left (Seating order: Alice, Bob, Charlie)</t>
+  </si>
+  <si>
+    <t>1. Bob is immediately to the right of Alice: [Alice, Bob].
+2. Alice is not on the far right (pos 3), so [Alice, Bob] must be in positions (1, 2).
+3. Charlie is in position 3. Therefore, Alice is on the far left.</t>
+  </si>
+  <si>
+    <t>You have a 3-liter jug and a 5-liter jug, and an unlimited supply of water. How can you measure out exactly 4 liters using only these two jugs without any measuring scales? Detail every pour step.</t>
+  </si>
+  <si>
+    <t>4 liters measured in the 5-liter jug</t>
+  </si>
+  <si>
+    <t>1. Fill 5L jug (5, 0) -&gt; Pour into 3L jug (2, 3) -&gt; Empty 3L jug (2, 0) -&gt; Transfer 2L to 3L jug (0, 2) -&gt; Fill 5L jug (5, 2) -&gt; Pour into 3L jug until full (leaving 4L in 5L jug) (4, 3).
+2. Detail state tracking after each pour.</t>
+  </si>
+  <si>
+    <t>On an island, inhabitants are either Knights (who always tell the truth) or Knaves (who always lie). You meet two inhabitants, A and B. A says: 'At least one of us is a Knave.' Determine precisely what A is and what B is. Provide a rigorous proof by cases.</t>
+  </si>
+  <si>
+    <t>A is a Knight, and B is a Knave</t>
+  </si>
+  <si>
+    <t>1. Case 1: Assume A is a Knave. A's claim ('At least one of us is a Knave') would be true, which is a contradiction since Knaves always lie.
+2. Therefore, A must be a Knight (truth-teller), so the claim is true.
+3. Since at least one is a Knave and A is a Knight, B must be a Knave.</t>
+  </si>
+  <si>
+    <t>Write a clean Python function `is_palindrome(s: str) -&gt; bool` that checks if a string is a palindrome, ignoring non-alphanumeric characters and case. Provide a brief trace of why it works.</t>
+  </si>
+  <si>
+    <t>is_palindrome(s: str) -&gt; bool filtering non-alphanumeric chars, lowercasing, and checking clean == clean[::-1]</t>
+  </si>
+  <si>
+    <t>1. Filter characters using .isalnum() and normalize case with .lower().
+2. Compare filtered sequence with reverse (or use two-pointer inward scan).
+3. Handles spaces, punctuation, and casing correctly.</t>
+  </si>
+  <si>
+    <t>Trace the execution of this Python code snippet and determine the exact printed output:
+x = [1, 2, 3]
+y = x
+y.append(4)
+print(len(x), x == y)
+Explain why `len(x)` is affected.</t>
+  </si>
+  <si>
+    <t>4 True</t>
+  </si>
+  <si>
+    <t>1. 'y = x' binds y to the exact same list object in memory (reference assignment, not copy).
+2. 'y.append(4)' mutates the shared list in place.
+3. Both x and y refer to [1, 2, 3, 4], so len(x) is 4 and x == y is True.</t>
+  </si>
+  <si>
+    <t>Identify the bug in the following binary search implementation and explain how to fix it:
+def binary_search(arr, target):
+    low = 0
+    high = len(arr)
+    while low &lt; high:
+        mid = (low + high) // 2
+        if arr[mid] == target:
+            return mid
+        elif arr[mid] &lt; target:
+            low = mid
+        else:
+            high = mid - 1
+    return -1</t>
+  </si>
+  <si>
+    <t>'low = mid' causes an infinite loop when high - low == 1 and arr[mid] &lt; target; fix with 'low = mid + 1'</t>
+  </si>
+  <si>
+    <t>1. Pinpoint infinite loop flaw: integer division (low + high) // 2 truncates, so low never increments if target &gt; arr[mid].
+2. Correct assignment: low = mid + 1.
+3. Align loop boundary condition with standard conventions.</t>
+  </si>
+  <si>
+    <t>Describe Floyd's Cycle-Finding Algorithm (Tortoise and Hare) for detecting a loop in a singly linked list. Explain why the time complexity is O(N) and the auxiliary space complexity is O(1).</t>
+  </si>
+  <si>
+    <t>Floyd's Cycle-Finding Algorithm (Tortoise &amp; Hare): O(N) time complexity, O(1) auxiliary space complexity</t>
+  </si>
+  <si>
+    <t>1. Slow pointer moves 1 step, fast pointer moves 2 steps.
+2. Relative speed of 1 node/step closes loop gap in at most loop length steps -&gt; O(N) time.
+3. Only two pointer references stored -&gt; O(1) space.</t>
+  </si>
+  <si>
+    <t>Propose an optimal algorithm in Python to find the Longest Increasing Subsequence (LIS) in O(N log N) time complexity using patience sorting / binary search. Provide the complete code, step-by-step invariant explanation, and complexity analysis.</t>
+  </si>
+  <si>
+    <t>O(N log N) Longest Increasing Subsequence (LIS) using patience sorting / binary search (bisect_left)</t>
+  </si>
+  <si>
+    <t>1. Maintain tails array where tails[i] stores the smallest tail element of all increasing subsequences of length i+1.
+2. Binary search to find insertion/replacement index.
+3. State loop invariant and explain O(N log N) time and O(N) auxiliary space.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2035,18 +2300,6 @@
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="36"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2068,7 +2321,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2091,56 +2344,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFE5E7EB"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFE5E7EB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFE5E7EB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFE5E7EB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFE5E7EB"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFE5E7EB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFE5E7EB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFE5E7EB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFE5E7EB"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFE5E7EB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFE5E7EB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFE5E7EB"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2162,39 +2370,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2497,7 +2677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:V46"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2505,7 +2685,7 @@
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="45" customWidth="1"/>
+    <col min="6" max="6" width="35" customWidth="1"/>
     <col min="7" max="7" width="48" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="23" customWidth="1"/>
@@ -2520,7 +2700,6 @@
     <col min="19" max="20" width="18" customWidth="1"/>
     <col min="21" max="21" width="26" customWidth="1"/>
     <col min="22" max="22" width="32" customWidth="1"/>
-    <col min="24" max="24" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="28.05" customHeight="1">
@@ -2591,7 +2770,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="39.6" customHeight="1">
+    <row r="2" spans="1:22" ht="19.95" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
@@ -2607,51 +2786,62 @@
       <c r="E2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D3</f>
+        <v>Solve for x: 3x + 12 = 30. Show each step of your calculation clearly and state the final numerical value of x.</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="2">
+        <v>2</v>
+      </c>
+      <c r="I2" s="2">
+        <v>2</v>
+      </c>
+      <c r="J2" s="2">
+        <v>2</v>
+      </c>
+      <c r="K2" s="2">
+        <v>2</v>
+      </c>
+      <c r="L2" s="2">
+        <f t="shared" ref="L2:L46" si="0">IF(COUNT(H2:K2)&gt;0, SUM(H2:K2), "")</f>
+        <v>8</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10" t="str">
-        <f t="shared" ref="L2:L46" si="0">IF(COUNT(H2:K2)&gt;0, SUM(H2:K2), "")</f>
-        <v/>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="10">
+      <c r="N2" s="2">
         <v>25.466000000000001</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="2">
         <v>18.619</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="2">
         <v>700</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="2">
         <f t="shared" ref="Q2:Q46" si="1">IF(AND(ISNUMBER(O2), O2&gt;0, ISNUMBER(P2)), ROUND(P2/O2, 2), IF(AND(ISNUMBER(N2), N2&gt;0, ISNUMBER(P2)), ROUND(P2/N2, 2), ""))</f>
         <v>37.6</v>
       </c>
-      <c r="R2" s="10">
+      <c r="R2" s="2">
         <v>3.64</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="S2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T2" s="10" t="s">
+      <c r="U2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="U2" s="9" t="s">
+      <c r="V2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="V2" s="9"/>
-    </row>
-    <row r="3" spans="1:22" ht="39.6" customHeight="1">
+    </row>
+    <row r="3" spans="1:22" ht="19.95" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>33</v>
       </c>
@@ -2667,59 +2857,70 @@
       <c r="E3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="F3" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D3</f>
+        <v>Solve for x: 3x + 12 = 30. Show each step of your calculation clearly and state the final numerical value of x.</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10" t="str">
+      <c r="H3" s="2">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2">
+        <v>2</v>
+      </c>
+      <c r="J3" s="2">
+        <v>2</v>
+      </c>
+      <c r="K3" s="2">
+        <v>2</v>
+      </c>
+      <c r="L3" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M3" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="2">
         <v>18.13</v>
       </c>
-      <c r="O3" s="10">
+      <c r="O3" s="2">
         <v>10.423</v>
       </c>
-      <c r="P3" s="10">
+      <c r="P3" s="2">
         <v>260</v>
       </c>
-      <c r="Q3" s="10">
+      <c r="Q3" s="2">
         <f t="shared" si="1"/>
         <v>24.94</v>
       </c>
-      <c r="R3" s="10">
+      <c r="R3" s="2">
         <v>4.53</v>
       </c>
-      <c r="S3" s="10" t="s">
+      <c r="S3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T3" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U3" s="9" t="s">
+      <c r="U3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="V3" s="9"/>
-    </row>
-    <row r="4" spans="1:22" ht="39.6" customHeight="1">
+      <c r="V3" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="19.95" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>25</v>
@@ -2727,56 +2928,67 @@
       <c r="E4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10" t="str">
+      <c r="F4" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D3</f>
+        <v>Solve for x: 3x + 12 = 30. Show each step of your calculation clearly and state the final numerical value of x.</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2</v>
+      </c>
+      <c r="I4" s="2">
+        <v>2</v>
+      </c>
+      <c r="J4" s="2">
+        <v>2</v>
+      </c>
+      <c r="K4" s="2">
+        <v>2</v>
+      </c>
+      <c r="L4" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M4" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="N4" s="10">
+        <v>8</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4" s="2">
         <v>32.939</v>
       </c>
-      <c r="O4" s="10">
+      <c r="O4" s="2">
         <v>28.401</v>
       </c>
-      <c r="P4" s="10">
+      <c r="P4" s="2">
         <v>863</v>
       </c>
-      <c r="Q4" s="10">
+      <c r="Q4" s="2">
         <f t="shared" si="1"/>
         <v>30.39</v>
       </c>
-      <c r="R4" s="10">
+      <c r="R4" s="2">
         <v>5.35</v>
       </c>
-      <c r="S4" s="10" t="s">
+      <c r="S4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T4" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U4" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="V4" s="9"/>
-    </row>
-    <row r="5" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="19.95" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>24</v>
@@ -2787,56 +2999,67 @@
       <c r="E5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10" t="str">
+      <c r="F5" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D4</f>
+        <v>A store offers a 20% discount on an item originally priced at $80. What is the final sale price? Show your work.</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="2">
+        <v>2</v>
+      </c>
+      <c r="I5" s="2">
+        <v>2</v>
+      </c>
+      <c r="J5" s="2">
+        <v>2</v>
+      </c>
+      <c r="K5" s="2">
+        <v>2</v>
+      </c>
+      <c r="L5" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M5" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="N5" s="10">
+        <v>8</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" s="2">
         <v>23.681999999999999</v>
       </c>
-      <c r="O5" s="10">
+      <c r="O5" s="2">
         <v>17.302</v>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="2">
         <v>627</v>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="2">
         <f t="shared" si="1"/>
         <v>36.24</v>
       </c>
-      <c r="R5" s="10">
+      <c r="R5" s="2">
         <v>3.64</v>
       </c>
-      <c r="S5" s="10" t="s">
+      <c r="S5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T5" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U5" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="V5" s="9"/>
-    </row>
-    <row r="6" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="19.95" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>34</v>
@@ -2847,59 +3070,70 @@
       <c r="E6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10" t="str">
+      <c r="F6" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D4</f>
+        <v>A store offers a 20% discount on an item originally priced at $80. What is the final sale price? Show your work.</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" s="2">
+        <v>2</v>
+      </c>
+      <c r="I6" s="2">
+        <v>2</v>
+      </c>
+      <c r="J6" s="2">
+        <v>2</v>
+      </c>
+      <c r="K6" s="2">
+        <v>2</v>
+      </c>
+      <c r="L6" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="N6" s="10">
+        <v>8</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N6" s="2">
         <v>15.942</v>
       </c>
-      <c r="O6" s="10">
+      <c r="O6" s="2">
         <v>8.4930000000000003</v>
       </c>
-      <c r="P6" s="10">
+      <c r="P6" s="2">
         <v>197</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="Q6" s="2">
         <f t="shared" si="1"/>
         <v>23.2</v>
       </c>
-      <c r="R6" s="10">
+      <c r="R6" s="2">
         <v>4.53</v>
       </c>
-      <c r="S6" s="10" t="s">
+      <c r="S6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T6" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U6" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="V6" s="9"/>
-    </row>
-    <row r="7" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="19.95" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>25</v>
@@ -2907,58 +3141,67 @@
       <c r="E7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10" t="str">
+      <c r="F7" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D4</f>
+        <v>A store offers a 20% discount on an item originally priced at $80. What is the final sale price? Show your work.</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="N7" s="10">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7" s="2">
         <v>41.906999999999996</v>
       </c>
-      <c r="O7" s="10">
+      <c r="O7" s="2">
         <v>33.497999999999998</v>
       </c>
-      <c r="P7" s="10">
+      <c r="P7" s="2">
         <v>1024</v>
       </c>
-      <c r="Q7" s="10">
+      <c r="Q7" s="2">
         <f t="shared" si="1"/>
         <v>30.57</v>
       </c>
-      <c r="R7" s="10">
+      <c r="R7" s="2">
         <v>5.35</v>
       </c>
-      <c r="S7" s="10" t="s">
+      <c r="S7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U7" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="V7" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="19.95" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>24</v>
@@ -2967,60 +3210,69 @@
         <v>25</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10" t="str">
+        <v>63</v>
+      </c>
+      <c r="F8" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D5</f>
+        <v>Calculate the total number of trailing zeroes in 100! (100 factorial). Explain the mathematical reasoning behind your method.</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="2">
+        <v>2</v>
+      </c>
+      <c r="I8" s="2">
+        <v>2</v>
+      </c>
+      <c r="J8" s="2">
+        <v>2</v>
+      </c>
+      <c r="K8" s="2">
+        <v>2</v>
+      </c>
+      <c r="L8" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="N8" s="10">
+        <v>8</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="N8" s="2">
         <v>30.957000000000001</v>
       </c>
-      <c r="O8" s="10">
+      <c r="O8" s="2">
         <v>26.738</v>
       </c>
-      <c r="P8" s="10">
+      <c r="P8" s="2">
         <v>1024</v>
       </c>
-      <c r="Q8" s="10">
+      <c r="Q8" s="2">
         <f t="shared" si="1"/>
         <v>38.299999999999997</v>
       </c>
-      <c r="R8" s="10">
+      <c r="R8" s="2">
         <v>3.64</v>
       </c>
-      <c r="S8" s="10" t="s">
+      <c r="S8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U8" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="V8" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="19.95" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>34</v>
@@ -3029,122 +3281,140 @@
         <v>25</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10" t="str">
+        <v>63</v>
+      </c>
+      <c r="F9" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D5</f>
+        <v>Calculate the total number of trailing zeroes in 100! (100 factorial). Explain the mathematical reasoning behind your method.</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M9" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="N9" s="10">
+        <v>3</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="N9" s="2">
         <v>36.115000000000002</v>
       </c>
-      <c r="O9" s="10">
+      <c r="O9" s="2">
         <v>31.943000000000001</v>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="2">
         <v>1024</v>
       </c>
-      <c r="Q9" s="10">
+      <c r="Q9" s="2">
         <f t="shared" si="1"/>
         <v>32.06</v>
       </c>
-      <c r="R9" s="10">
+      <c r="R9" s="2">
         <v>4.53</v>
       </c>
-      <c r="S9" s="10" t="s">
+      <c r="S9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T9" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U9" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="V9" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="19.95" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10" t="str">
+        <v>63</v>
+      </c>
+      <c r="F10" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D5</f>
+        <v>Calculate the total number of trailing zeroes in 100! (100 factorial). Explain the mathematical reasoning behind your method.</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="N10" s="10">
+        <v>3</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="N10" s="2">
         <v>41.31</v>
       </c>
-      <c r="O10" s="10">
+      <c r="O10" s="2">
         <v>33.244999999999997</v>
       </c>
-      <c r="P10" s="10">
+      <c r="P10" s="2">
         <v>1024</v>
       </c>
-      <c r="Q10" s="10">
+      <c r="Q10" s="2">
         <f t="shared" si="1"/>
         <v>30.8</v>
       </c>
-      <c r="R10" s="10">
+      <c r="R10" s="2">
         <v>5.35</v>
       </c>
-      <c r="S10" s="10" t="s">
+      <c r="S10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U10" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="V10" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U10" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="19.95" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>24</v>
@@ -3153,60 +3423,69 @@
         <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10" t="str">
+        <v>63</v>
+      </c>
+      <c r="F11" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D6</f>
+        <v>Find the next two numbers in the sequence: 2, 6, 12, 20, 30, ... Explain the underlying rule governing the pattern.</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="N11" s="10">
+        <v>3</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N11" s="2">
         <v>31.045000000000002</v>
       </c>
-      <c r="O11" s="10">
+      <c r="O11" s="2">
         <v>26.792999999999999</v>
       </c>
-      <c r="P11" s="10">
+      <c r="P11" s="2">
         <v>1024</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="Q11" s="2">
         <f t="shared" si="1"/>
         <v>38.22</v>
       </c>
-      <c r="R11" s="10">
+      <c r="R11" s="2">
         <v>3.64</v>
       </c>
-      <c r="S11" s="10" t="s">
+      <c r="S11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U11" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="V11" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="19.95" customHeight="1">
       <c r="A12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>34</v>
@@ -3215,120 +3494,140 @@
         <v>25</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10" t="str">
+        <v>63</v>
+      </c>
+      <c r="F12" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D6</f>
+        <v>Find the next two numbers in the sequence: 2, 6, 12, 20, 30, ... Explain the underlying rule governing the pattern.</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" s="2">
+        <v>2</v>
+      </c>
+      <c r="I12" s="2">
+        <v>2</v>
+      </c>
+      <c r="J12" s="2">
+        <v>2</v>
+      </c>
+      <c r="K12" s="2">
+        <v>2</v>
+      </c>
+      <c r="L12" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="N12" s="10">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N12" s="2">
         <v>23.050999999999998</v>
       </c>
-      <c r="O12" s="10">
+      <c r="O12" s="2">
         <v>18.898</v>
       </c>
-      <c r="P12" s="10">
+      <c r="P12" s="2">
         <v>571</v>
       </c>
-      <c r="Q12" s="10">
+      <c r="Q12" s="2">
         <f t="shared" si="1"/>
         <v>30.21</v>
       </c>
-      <c r="R12" s="10">
+      <c r="R12" s="2">
         <v>4.53</v>
       </c>
-      <c r="S12" s="10" t="s">
+      <c r="S12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T12" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U12" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="V12" s="9"/>
-    </row>
-    <row r="13" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="19.95" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10" t="str">
+        <v>63</v>
+      </c>
+      <c r="F13" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D6</f>
+        <v>Find the next two numbers in the sequence: 2, 6, 12, 20, 30, ... Explain the underlying rule governing the pattern.</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="N13" s="10">
+        <v>3</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="N13" s="2">
         <v>37.543999999999997</v>
       </c>
-      <c r="O13" s="10">
+      <c r="O13" s="2">
         <v>33.052999999999997</v>
       </c>
-      <c r="P13" s="10">
+      <c r="P13" s="2">
         <v>1024</v>
       </c>
-      <c r="Q13" s="10">
+      <c r="Q13" s="2">
         <f t="shared" si="1"/>
         <v>30.98</v>
       </c>
-      <c r="R13" s="10">
+      <c r="R13" s="2">
         <v>5.35</v>
       </c>
-      <c r="S13" s="10" t="s">
+      <c r="S13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U13" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="V13" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="V13" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="19.95" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>24</v>
@@ -3337,60 +3636,69 @@
         <v>25</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10" t="str">
+        <v>96</v>
+      </c>
+      <c r="F14" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D7</f>
+        <v>Three fair standard six-sided dice are rolled simultaneously. What is the exact probability that the sum of the numbers rolled is equal to 10? Express your answer as a simplified fraction and explain each step.</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="N14" s="10">
+        <v>3</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="N14" s="2">
         <v>30.626999999999999</v>
       </c>
-      <c r="O14" s="10">
+      <c r="O14" s="2">
         <v>26.364000000000001</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P14" s="2">
         <v>1024</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="Q14" s="2">
         <f t="shared" si="1"/>
         <v>38.840000000000003</v>
       </c>
-      <c r="R14" s="10">
+      <c r="R14" s="2">
         <v>3.64</v>
       </c>
-      <c r="S14" s="10" t="s">
+      <c r="S14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T14" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U14" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="V14" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U14" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="19.95" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>34</v>
@@ -3399,2022 +3707,2316 @@
         <v>25</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10" t="str">
+        <v>96</v>
+      </c>
+      <c r="F15" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D7</f>
+        <v>Three fair standard six-sided dice are rolled simultaneously. What is the exact probability that the sum of the numbers rolled is equal to 10? Express your answer as a simplified fraction and explain each step.</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="N15" s="10">
+        <v>3</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N15" s="2">
         <v>35.292000000000002</v>
       </c>
-      <c r="O15" s="10">
+      <c r="O15" s="2">
         <v>31.119</v>
       </c>
-      <c r="P15" s="10">
+      <c r="P15" s="2">
         <v>1024</v>
       </c>
-      <c r="Q15" s="10">
+      <c r="Q15" s="2">
         <f t="shared" si="1"/>
         <v>32.909999999999997</v>
       </c>
-      <c r="R15" s="10">
+      <c r="R15" s="2">
         <v>4.53</v>
       </c>
-      <c r="S15" s="10" t="s">
+      <c r="S15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T15" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U15" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="V15" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U15" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="19.95" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10" t="str">
+        <v>96</v>
+      </c>
+      <c r="F16" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D7</f>
+        <v>Three fair standard six-sided dice are rolled simultaneously. What is the exact probability that the sum of the numbers rolled is equal to 10? Express your answer as a simplified fraction and explain each step.</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M16" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="N16" s="10">
+        <v>3</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="N16" s="2">
         <v>37.811</v>
       </c>
-      <c r="O16" s="10">
+      <c r="O16" s="2">
         <v>33.268999999999998</v>
       </c>
-      <c r="P16" s="10">
+      <c r="P16" s="2">
         <v>1024</v>
       </c>
-      <c r="Q16" s="10">
+      <c r="Q16" s="2">
         <f t="shared" si="1"/>
         <v>30.78</v>
       </c>
-      <c r="R16" s="10">
+      <c r="R16" s="2">
         <v>5.35</v>
       </c>
-      <c r="S16" s="10" t="s">
+      <c r="S16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T16" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U16" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="V16" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U16" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="19.95" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10" t="str">
+      <c r="F17" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D8</f>
+        <v>A farmer has 17 sheep, and all but 9 die. How many live sheep does the farmer have left? State your answer and briefly explain the logic.</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H17" s="2">
+        <v>2</v>
+      </c>
+      <c r="I17" s="2">
+        <v>2</v>
+      </c>
+      <c r="J17" s="2">
+        <v>2</v>
+      </c>
+      <c r="K17" s="2">
+        <v>2</v>
+      </c>
+      <c r="L17" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M17" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="N17" s="10">
+        <v>8</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="N17" s="2">
         <v>23.832999999999998</v>
       </c>
-      <c r="O17" s="10">
+      <c r="O17" s="2">
         <v>16.919</v>
       </c>
-      <c r="P17" s="10">
+      <c r="P17" s="2">
         <v>662</v>
       </c>
-      <c r="Q17" s="10">
+      <c r="Q17" s="2">
         <f t="shared" si="1"/>
         <v>39.130000000000003</v>
       </c>
-      <c r="R17" s="10">
+      <c r="R17" s="2">
         <v>3.64</v>
       </c>
-      <c r="S17" s="10" t="s">
+      <c r="S17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T17" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U17" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="V17" s="9"/>
-    </row>
-    <row r="18" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="19.95" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10" t="str">
+      <c r="F18" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D8</f>
+        <v>A farmer has 17 sheep, and all but 9 die. How many live sheep does the farmer have left? State your answer and briefly explain the logic.</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H18" s="2">
+        <v>2</v>
+      </c>
+      <c r="I18" s="2">
+        <v>2</v>
+      </c>
+      <c r="J18" s="2">
+        <v>2</v>
+      </c>
+      <c r="K18" s="2">
+        <v>2</v>
+      </c>
+      <c r="L18" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M18" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="N18" s="10">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="N18" s="2">
         <v>13.25</v>
       </c>
-      <c r="O18" s="10">
+      <c r="O18" s="2">
         <v>9.0380000000000003</v>
       </c>
-      <c r="P18" s="10">
+      <c r="P18" s="2">
         <v>217</v>
       </c>
-      <c r="Q18" s="10">
+      <c r="Q18" s="2">
         <f t="shared" si="1"/>
         <v>24.01</v>
       </c>
-      <c r="R18" s="10">
+      <c r="R18" s="2">
         <v>4.53</v>
       </c>
-      <c r="S18" s="10" t="s">
+      <c r="S18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T18" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U18" s="9" t="s">
+      <c r="U18" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="19.95" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="V18" s="9"/>
-    </row>
-    <row r="19" spans="1:22" ht="39.6" customHeight="1">
-      <c r="A19" s="2" t="s">
+      <c r="C19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10" t="str">
+      <c r="F19" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D8</f>
+        <v>A farmer has 17 sheep, and all but 9 die. How many live sheep does the farmer have left? State your answer and briefly explain the logic.</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H19" s="2">
+        <v>2</v>
+      </c>
+      <c r="I19" s="2">
+        <v>2</v>
+      </c>
+      <c r="J19" s="2">
+        <v>2</v>
+      </c>
+      <c r="K19" s="2">
+        <v>2</v>
+      </c>
+      <c r="L19" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M19" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="N19" s="10">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N19" s="2">
         <v>40.401000000000003</v>
       </c>
-      <c r="O19" s="10">
+      <c r="O19" s="2">
         <v>31.734000000000002</v>
       </c>
-      <c r="P19" s="10">
+      <c r="P19" s="2">
         <v>995</v>
       </c>
-      <c r="Q19" s="10">
+      <c r="Q19" s="2">
         <f t="shared" si="1"/>
         <v>31.35</v>
       </c>
-      <c r="R19" s="10">
+      <c r="R19" s="2">
         <v>5.35</v>
       </c>
-      <c r="S19" s="10" t="s">
+      <c r="S19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T19" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U19" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="V19" s="9"/>
-    </row>
-    <row r="20" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U19" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="19.95" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F20" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10" t="str">
+      <c r="F20" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D9</f>
+        <v>All roses are flowers. Some flowers fade quickly. Does it strictly follow that some roses fade quickly? Answer with 'Yes' or 'No' and provide a formal logical justification.</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H20" s="2">
+        <v>2</v>
+      </c>
+      <c r="I20" s="2">
+        <v>2</v>
+      </c>
+      <c r="J20" s="2">
+        <v>2</v>
+      </c>
+      <c r="K20" s="2">
+        <v>2</v>
+      </c>
+      <c r="L20" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M20" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="N20" s="10">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="N20" s="2">
         <v>33.518000000000001</v>
       </c>
-      <c r="O20" s="10">
+      <c r="O20" s="2">
         <v>26.882000000000001</v>
       </c>
-      <c r="P20" s="10">
+      <c r="P20" s="2">
         <v>1024</v>
       </c>
-      <c r="Q20" s="10">
+      <c r="Q20" s="2">
         <f t="shared" si="1"/>
         <v>38.090000000000003</v>
       </c>
-      <c r="R20" s="10">
+      <c r="R20" s="2">
         <v>3.64</v>
       </c>
-      <c r="S20" s="10" t="s">
+      <c r="S20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T20" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T20" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U20" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="V20" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U20" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="19.95" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F21" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10" t="str">
+      <c r="F21" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D9</f>
+        <v>All roses are flowers. Some flowers fade quickly. Does it strictly follow that some roses fade quickly? Answer with 'Yes' or 'No' and provide a formal logical justification.</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2">
+        <v>1</v>
+      </c>
+      <c r="K21" s="2">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M21" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="N21" s="10">
+        <v>3</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="N21" s="2">
         <v>31.620999999999999</v>
       </c>
-      <c r="O21" s="10">
+      <c r="O21" s="2">
         <v>24.053000000000001</v>
       </c>
-      <c r="P21" s="10">
+      <c r="P21" s="2">
         <v>742</v>
       </c>
-      <c r="Q21" s="10">
+      <c r="Q21" s="2">
         <f t="shared" si="1"/>
         <v>30.85</v>
       </c>
-      <c r="R21" s="10">
+      <c r="R21" s="2">
         <v>4.53</v>
       </c>
-      <c r="S21" s="10" t="s">
+      <c r="S21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T21" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U21" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="V21" s="9"/>
-    </row>
-    <row r="22" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U21" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="19.95" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F22" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10" t="str">
+      <c r="F22" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D9</f>
+        <v>All roses are flowers. Some flowers fade quickly. Does it strictly follow that some roses fade quickly? Answer with 'Yes' or 'No' and provide a formal logical justification.</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H22" s="2">
+        <v>2</v>
+      </c>
+      <c r="I22" s="2">
+        <v>2</v>
+      </c>
+      <c r="J22" s="2">
+        <v>2</v>
+      </c>
+      <c r="K22" s="2">
+        <v>2</v>
+      </c>
+      <c r="L22" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="N22" s="10">
+        <v>8</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="N22" s="2">
         <v>28.545000000000002</v>
       </c>
-      <c r="O22" s="10">
+      <c r="O22" s="2">
         <v>23.701000000000001</v>
       </c>
-      <c r="P22" s="10">
+      <c r="P22" s="2">
         <v>716</v>
       </c>
-      <c r="Q22" s="10">
+      <c r="Q22" s="2">
         <f t="shared" si="1"/>
         <v>30.21</v>
       </c>
-      <c r="R22" s="10">
+      <c r="R22" s="2">
         <v>5.35</v>
       </c>
-      <c r="S22" s="10" t="s">
+      <c r="S22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T22" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T22" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U22" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="V22" s="9"/>
-    </row>
-    <row r="23" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U22" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="19.95" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10" t="str">
+        <v>63</v>
+      </c>
+      <c r="F23" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D10</f>
+        <v>Alice, Bob, and Charlie are sitting in a row. Alice is not on the far right. Bob is sitting to the immediate right of Alice. Who is sitting on the far left? Deduce the exact left-to-right seating arrangement step by step.</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>1</v>
+      </c>
+      <c r="J23" s="2">
+        <v>1</v>
+      </c>
+      <c r="K23" s="2">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M23" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="N23" s="10">
+        <v>3</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="N23" s="2">
         <v>31.611000000000001</v>
       </c>
-      <c r="O23" s="10">
+      <c r="O23" s="2">
         <v>27.300999999999998</v>
       </c>
-      <c r="P23" s="10">
+      <c r="P23" s="2">
         <v>1024</v>
       </c>
-      <c r="Q23" s="10">
+      <c r="Q23" s="2">
         <f t="shared" si="1"/>
         <v>37.51</v>
       </c>
-      <c r="R23" s="10">
+      <c r="R23" s="2">
         <v>3.64</v>
       </c>
-      <c r="S23" s="10" t="s">
+      <c r="S23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T23" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U23" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="V23" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U23" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="19.95" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10" t="str">
+        <v>63</v>
+      </c>
+      <c r="F24" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D10</f>
+        <v>Alice, Bob, and Charlie are sitting in a row. Alice is not on the far right. Bob is sitting to the immediate right of Alice. Who is sitting on the far left? Deduce the exact left-to-right seating arrangement step by step.</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H24" s="2">
+        <v>2</v>
+      </c>
+      <c r="I24" s="2">
+        <v>2</v>
+      </c>
+      <c r="J24" s="2">
+        <v>2</v>
+      </c>
+      <c r="K24" s="2">
+        <v>2</v>
+      </c>
+      <c r="L24" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M24" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="N24" s="10">
+        <v>8</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="N24" s="2">
         <v>22.279</v>
       </c>
-      <c r="O24" s="10">
+      <c r="O24" s="2">
         <v>14.8</v>
       </c>
-      <c r="P24" s="10">
+      <c r="P24" s="2">
         <v>412</v>
       </c>
-      <c r="Q24" s="10">
+      <c r="Q24" s="2">
         <f t="shared" si="1"/>
         <v>27.84</v>
       </c>
-      <c r="R24" s="10">
+      <c r="R24" s="2">
         <v>4.53</v>
       </c>
-      <c r="S24" s="10" t="s">
+      <c r="S24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T24" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T24" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U24" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="V24" s="9"/>
-    </row>
-    <row r="25" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U24" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="19.95" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10" t="str">
+        <v>63</v>
+      </c>
+      <c r="F25" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D10</f>
+        <v>Alice, Bob, and Charlie are sitting in a row. Alice is not on the far right. Bob is sitting to the immediate right of Alice. Who is sitting on the far left? Deduce the exact left-to-right seating arrangement step by step.</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
+        <v>1</v>
+      </c>
+      <c r="J25" s="2">
+        <v>1</v>
+      </c>
+      <c r="K25" s="2">
+        <v>1</v>
+      </c>
+      <c r="L25" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="N25" s="10">
+        <v>3</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="N25" s="2">
         <v>36.968000000000004</v>
       </c>
-      <c r="O25" s="10">
+      <c r="O25" s="2">
         <v>32.411999999999999</v>
       </c>
-      <c r="P25" s="10">
+      <c r="P25" s="2">
         <v>1024</v>
       </c>
-      <c r="Q25" s="10">
+      <c r="Q25" s="2">
         <f t="shared" si="1"/>
         <v>31.59</v>
       </c>
-      <c r="R25" s="10">
+      <c r="R25" s="2">
         <v>5.35</v>
       </c>
-      <c r="S25" s="10" t="s">
+      <c r="S25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T25" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T25" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U25" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="V25" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U25" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="V25" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="19.95" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F26" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10" t="str">
+        <v>63</v>
+      </c>
+      <c r="F26" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D11</f>
+        <v>You have a 3-liter jug and a 5-liter jug, and an unlimited supply of water. How can you measure out exactly 4 liters using only these two jugs without any measuring scales? Detail every pour step.</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <v>1</v>
+      </c>
+      <c r="J26" s="2">
+        <v>1</v>
+      </c>
+      <c r="K26" s="2">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M26" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="N26" s="10">
+        <v>3</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="N26" s="2">
         <v>30.733000000000001</v>
       </c>
-      <c r="O26" s="10">
+      <c r="O26" s="2">
         <v>26.405000000000001</v>
       </c>
-      <c r="P26" s="10">
+      <c r="P26" s="2">
         <v>1024</v>
       </c>
-      <c r="Q26" s="10">
+      <c r="Q26" s="2">
         <f t="shared" si="1"/>
         <v>38.78</v>
       </c>
-      <c r="R26" s="10">
+      <c r="R26" s="2">
         <v>3.64</v>
       </c>
-      <c r="S26" s="10" t="s">
+      <c r="S26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T26" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T26" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U26" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="V26" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U26" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="19.95" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10" t="str">
+        <v>63</v>
+      </c>
+      <c r="F27" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D11</f>
+        <v>You have a 3-liter jug and a 5-liter jug, and an unlimited supply of water. How can you measure out exactly 4 liters using only these two jugs without any measuring scales? Detail every pour step.</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H27" s="2">
+        <v>2</v>
+      </c>
+      <c r="I27" s="2">
+        <v>2</v>
+      </c>
+      <c r="J27" s="2">
+        <v>2</v>
+      </c>
+      <c r="K27" s="2">
+        <v>2</v>
+      </c>
+      <c r="L27" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M27" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="N27" s="10">
+        <v>8</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="N27" s="2">
         <v>25.206</v>
       </c>
-      <c r="O27" s="10">
+      <c r="O27" s="2">
         <v>21.076000000000001</v>
       </c>
-      <c r="P27" s="10">
+      <c r="P27" s="2">
         <v>652</v>
       </c>
-      <c r="Q27" s="10">
+      <c r="Q27" s="2">
         <f t="shared" si="1"/>
         <v>30.94</v>
       </c>
-      <c r="R27" s="10">
+      <c r="R27" s="2">
         <v>4.53</v>
       </c>
-      <c r="S27" s="10" t="s">
+      <c r="S27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T27" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U27" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="V27" s="9"/>
-    </row>
-    <row r="28" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U27" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="19.95" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10" t="str">
+        <v>63</v>
+      </c>
+      <c r="F28" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D11</f>
+        <v>You have a 3-liter jug and a 5-liter jug, and an unlimited supply of water. How can you measure out exactly 4 liters using only these two jugs without any measuring scales? Detail every pour step.</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
+        <v>1</v>
+      </c>
+      <c r="J28" s="2">
+        <v>1</v>
+      </c>
+      <c r="K28" s="2">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M28" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="N28" s="10">
+        <v>3</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="N28" s="2">
         <v>41.716999999999999</v>
       </c>
-      <c r="O28" s="10">
+      <c r="O28" s="2">
         <v>33.280999999999999</v>
       </c>
-      <c r="P28" s="10">
+      <c r="P28" s="2">
         <v>1024</v>
       </c>
-      <c r="Q28" s="10">
+      <c r="Q28" s="2">
         <f t="shared" si="1"/>
         <v>30.77</v>
       </c>
-      <c r="R28" s="10">
+      <c r="R28" s="2">
         <v>5.35</v>
       </c>
-      <c r="S28" s="10" t="s">
+      <c r="S28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T28" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T28" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U28" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="V28" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U28" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="V28" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="19.95" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F29" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10" t="str">
+        <v>96</v>
+      </c>
+      <c r="F29" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D12</f>
+        <v>On an island, inhabitants are either Knights (who always tell the truth) or Knaves (who always lie). You meet two inhabitants, A and B. A says: 'At least one of us is a Knave.' Determine precisely what A is and what B is. Provide a rigorous proof by cases.</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H29" s="2">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2">
+        <v>1</v>
+      </c>
+      <c r="J29" s="2">
+        <v>1</v>
+      </c>
+      <c r="K29" s="2">
+        <v>1</v>
+      </c>
+      <c r="L29" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M29" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="N29" s="10">
+        <v>3</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="N29" s="2">
         <v>32.633000000000003</v>
       </c>
-      <c r="O29" s="10">
+      <c r="O29" s="2">
         <v>25.693999999999999</v>
       </c>
-      <c r="P29" s="10">
+      <c r="P29" s="2">
         <v>1024</v>
       </c>
-      <c r="Q29" s="10">
+      <c r="Q29" s="2">
         <f t="shared" si="1"/>
         <v>39.85</v>
       </c>
-      <c r="R29" s="10">
+      <c r="R29" s="2">
         <v>3.64</v>
       </c>
-      <c r="S29" s="10" t="s">
+      <c r="S29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T29" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T29" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U29" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="V29" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U29" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="19.95" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10" t="str">
+        <v>96</v>
+      </c>
+      <c r="F30" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D12</f>
+        <v>On an island, inhabitants are either Knights (who always tell the truth) or Knaves (who always lie). You meet two inhabitants, A and B. A says: 'At least one of us is a Knave.' Determine precisely what A is and what B is. Provide a rigorous proof by cases.</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H30" s="2">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2">
+        <v>1</v>
+      </c>
+      <c r="J30" s="2">
+        <v>1</v>
+      </c>
+      <c r="K30" s="2">
+        <v>1</v>
+      </c>
+      <c r="L30" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M30" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="N30" s="10">
+        <v>3</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="N30" s="2">
         <v>35.985999999999997</v>
       </c>
-      <c r="O30" s="10">
+      <c r="O30" s="2">
         <v>31.789000000000001</v>
       </c>
-      <c r="P30" s="10">
+      <c r="P30" s="2">
         <v>1024</v>
       </c>
-      <c r="Q30" s="10">
+      <c r="Q30" s="2">
         <f t="shared" si="1"/>
         <v>32.21</v>
       </c>
-      <c r="R30" s="10">
+      <c r="R30" s="2">
         <v>4.54</v>
       </c>
-      <c r="S30" s="10" t="s">
+      <c r="S30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T30" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T30" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U30" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="V30" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U30" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="V30" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="19.95" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10" t="str">
+        <v>96</v>
+      </c>
+      <c r="F31" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D12</f>
+        <v>On an island, inhabitants are either Knights (who always tell the truth) or Knaves (who always lie). You meet two inhabitants, A and B. A says: 'At least one of us is a Knave.' Determine precisely what A is and what B is. Provide a rigorous proof by cases.</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
+        <v>1</v>
+      </c>
+      <c r="J31" s="2">
+        <v>1</v>
+      </c>
+      <c r="K31" s="2">
+        <v>1</v>
+      </c>
+      <c r="L31" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M31" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="N31" s="10">
+        <v>3</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="N31" s="2">
         <v>41.253999999999998</v>
       </c>
-      <c r="O31" s="10">
+      <c r="O31" s="2">
         <v>33.155999999999999</v>
       </c>
-      <c r="P31" s="10">
+      <c r="P31" s="2">
         <v>1024</v>
       </c>
-      <c r="Q31" s="10">
+      <c r="Q31" s="2">
         <f t="shared" si="1"/>
         <v>30.88</v>
       </c>
-      <c r="R31" s="10">
+      <c r="R31" s="2">
         <v>5.35</v>
       </c>
-      <c r="S31" s="10" t="s">
+      <c r="S31" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T31" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T31" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U31" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="V31" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U31" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="V31" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="19.95" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F32" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15" t="str">
+      <c r="F32" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D13</f>
+        <v>Write a clean Python function `is_palindrome(s: str) -&gt; bool` that checks if a string is a palindrome, ignoring non-alphanumeric characters and case. Provide a brief trace of why it works.</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H32" s="2">
+        <v>2</v>
+      </c>
+      <c r="I32" s="2">
+        <v>2</v>
+      </c>
+      <c r="J32" s="2">
+        <v>2</v>
+      </c>
+      <c r="K32" s="2">
+        <v>2</v>
+      </c>
+      <c r="L32" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M32" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="N32" s="15">
+        <v>8</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="N32" s="2">
         <v>34.549999999999997</v>
       </c>
-      <c r="O32" s="15">
+      <c r="O32" s="2">
         <v>27.591000000000001</v>
       </c>
-      <c r="P32" s="15">
+      <c r="P32" s="2">
         <v>1024</v>
       </c>
-      <c r="Q32" s="15">
+      <c r="Q32" s="2">
         <f t="shared" si="1"/>
         <v>37.11</v>
       </c>
-      <c r="R32" s="15">
+      <c r="R32" s="2">
         <v>3.64</v>
       </c>
-      <c r="S32" s="15" t="s">
+      <c r="S32" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T32" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T32" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="U32" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="V32" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U32" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="19.95" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F33" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="G33" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15" t="str">
+      <c r="F33" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D13</f>
+        <v>Write a clean Python function `is_palindrome(s: str) -&gt; bool` that checks if a string is a palindrome, ignoring non-alphanumeric characters and case. Provide a brief trace of why it works.</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H33" s="2">
+        <v>0</v>
+      </c>
+      <c r="I33" s="2">
+        <v>1</v>
+      </c>
+      <c r="J33" s="2">
+        <v>1</v>
+      </c>
+      <c r="K33" s="2">
+        <v>1</v>
+      </c>
+      <c r="L33" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M33" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="N33" s="15">
+        <v>3</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="N33" s="2">
         <v>40.799999999999997</v>
       </c>
-      <c r="O33" s="15">
+      <c r="O33" s="2">
         <v>32.722999999999999</v>
       </c>
-      <c r="P33" s="15">
+      <c r="P33" s="2">
         <v>1024</v>
       </c>
-      <c r="Q33" s="15">
+      <c r="Q33" s="2">
         <f t="shared" si="1"/>
         <v>31.29</v>
       </c>
-      <c r="R33" s="15">
+      <c r="R33" s="2">
         <v>4.53</v>
       </c>
-      <c r="S33" s="15" t="s">
+      <c r="S33" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T33" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T33" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="U33" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="V33" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U33" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="19.95" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F34" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15" t="str">
+      <c r="F34" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D13</f>
+        <v>Write a clean Python function `is_palindrome(s: str) -&gt; bool` that checks if a string is a palindrome, ignoring non-alphanumeric characters and case. Provide a brief trace of why it works.</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="H34" s="2">
+        <v>0</v>
+      </c>
+      <c r="I34" s="2">
+        <v>1</v>
+      </c>
+      <c r="J34" s="2">
+        <v>1</v>
+      </c>
+      <c r="K34" s="2">
+        <v>1</v>
+      </c>
+      <c r="L34" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M34" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="N34" s="15">
+        <v>3</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="N34" s="2">
         <v>42.369</v>
       </c>
-      <c r="O34" s="15">
+      <c r="O34" s="2">
         <v>33.698</v>
       </c>
-      <c r="P34" s="15">
+      <c r="P34" s="2">
         <v>1024</v>
       </c>
-      <c r="Q34" s="15">
+      <c r="Q34" s="2">
         <f t="shared" si="1"/>
         <v>30.39</v>
       </c>
-      <c r="R34" s="15">
+      <c r="R34" s="2">
         <v>5.35</v>
       </c>
-      <c r="S34" s="15" t="s">
+      <c r="S34" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T34" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T34" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="U34" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="V34" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U34" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="V34" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="19.95" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F35" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="G35" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15" t="str">
+      <c r="F35" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D14</f>
+        <v>Trace the execution of this Python code snippet and determine the exact printed output:
+x = [1, 2, 3]
+y = x
+y.append(4)
+print(len(x), x == y)
+Explain why `len(x)` is affected.</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H35" s="2">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2">
+        <v>1</v>
+      </c>
+      <c r="K35" s="2">
+        <v>1</v>
+      </c>
+      <c r="L35" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M35" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="N35" s="15">
+        <v>3</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="N35" s="2">
         <v>26.28</v>
       </c>
-      <c r="O35" s="15">
+      <c r="O35" s="2">
         <v>22.030999999999999</v>
       </c>
-      <c r="P35" s="15">
+      <c r="P35" s="2">
         <v>792</v>
       </c>
-      <c r="Q35" s="15">
+      <c r="Q35" s="2">
         <f t="shared" si="1"/>
         <v>35.950000000000003</v>
       </c>
-      <c r="R35" s="15">
+      <c r="R35" s="2">
         <v>3.64</v>
       </c>
-      <c r="S35" s="15" t="s">
+      <c r="S35" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T35" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T35" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="U35" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="V35" s="14"/>
-    </row>
-    <row r="36" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U35" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="19.95" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F36" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="G36" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15" t="str">
+      <c r="F36" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D14</f>
+        <v>Trace the execution of this Python code snippet and determine the exact printed output:
+x = [1, 2, 3]
+y = x
+y.append(4)
+print(len(x), x == y)
+Explain why `len(x)` is affected.</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="H36" s="2">
+        <v>2</v>
+      </c>
+      <c r="I36" s="2">
+        <v>2</v>
+      </c>
+      <c r="J36" s="2">
+        <v>2</v>
+      </c>
+      <c r="K36" s="2">
+        <v>2</v>
+      </c>
+      <c r="L36" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M36" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="N36" s="15">
+        <v>8</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="N36" s="2">
         <v>27.274000000000001</v>
       </c>
-      <c r="O36" s="15">
+      <c r="O36" s="2">
         <v>19.149999999999999</v>
       </c>
-      <c r="P36" s="15">
+      <c r="P36" s="2">
         <v>540</v>
       </c>
-      <c r="Q36" s="15">
+      <c r="Q36" s="2">
         <f t="shared" si="1"/>
         <v>28.2</v>
       </c>
-      <c r="R36" s="15">
+      <c r="R36" s="2">
         <v>4.53</v>
       </c>
-      <c r="S36" s="15" t="s">
+      <c r="S36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T36" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T36" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="U36" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="V36" s="14"/>
-    </row>
-    <row r="37" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U36" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="V36" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="19.95" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F37" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="G37" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15" t="str">
+      <c r="F37" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D14</f>
+        <v>Trace the execution of this Python code snippet and determine the exact printed output:
+x = [1, 2, 3]
+y = x
+y.append(4)
+print(len(x), x == y)
+Explain why `len(x)` is affected.</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="H37" s="2">
+        <v>2</v>
+      </c>
+      <c r="I37" s="2">
+        <v>2</v>
+      </c>
+      <c r="J37" s="2">
+        <v>2</v>
+      </c>
+      <c r="K37" s="2">
+        <v>2</v>
+      </c>
+      <c r="L37" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M37" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="N37" s="15">
+        <v>8</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="N37" s="2">
         <v>35.694000000000003</v>
       </c>
-      <c r="O37" s="15">
+      <c r="O37" s="2">
         <v>31.201000000000001</v>
       </c>
-      <c r="P37" s="15">
+      <c r="P37" s="2">
         <v>907</v>
       </c>
-      <c r="Q37" s="15">
+      <c r="Q37" s="2">
         <f t="shared" si="1"/>
         <v>29.07</v>
       </c>
-      <c r="R37" s="15">
+      <c r="R37" s="2">
         <v>5.35</v>
       </c>
-      <c r="S37" s="15" t="s">
+      <c r="S37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T37" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T37" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="U37" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="V37" s="14"/>
-    </row>
-    <row r="38" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U37" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="V37" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" ht="19.95" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F38" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15" t="str">
+        <v>63</v>
+      </c>
+      <c r="F38" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D15</f>
+        <v>Identify the bug in the following binary search implementation and explain how to fix it:
+def binary_search(arr, target):
+    low = 0
+    high = len(arr)
+    while low &lt; high:
+        mid = (low + high) // 2
+        if arr[mid] == target:
+            return mid
+        elif arr[mid] &lt; target:
+            low = mid
+        else:
+            high = mid - 1
+    return -1</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2">
+        <v>1</v>
+      </c>
+      <c r="J38" s="2">
+        <v>1</v>
+      </c>
+      <c r="K38" s="2">
+        <v>1</v>
+      </c>
+      <c r="L38" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M38" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="N38" s="15">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="N38" s="2">
         <v>34.47</v>
       </c>
-      <c r="O38" s="15">
+      <c r="O38" s="2">
         <v>27.48</v>
       </c>
-      <c r="P38" s="15">
+      <c r="P38" s="2">
         <v>1024</v>
       </c>
-      <c r="Q38" s="15">
+      <c r="Q38" s="2">
         <f t="shared" si="1"/>
         <v>37.26</v>
       </c>
-      <c r="R38" s="15">
+      <c r="R38" s="2">
         <v>3.64</v>
       </c>
-      <c r="S38" s="15" t="s">
+      <c r="S38" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T38" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T38" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="U38" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="V38" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U38" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="V38" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" ht="19.95" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F39" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="G39" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15" t="str">
+        <v>63</v>
+      </c>
+      <c r="F39" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D15</f>
+        <v>Identify the bug in the following binary search implementation and explain how to fix it:
+def binary_search(arr, target):
+    low = 0
+    high = len(arr)
+    while low &lt; high:
+        mid = (low + high) // 2
+        if arr[mid] == target:
+            return mid
+        elif arr[mid] &lt; target:
+            low = mid
+        else:
+            high = mid - 1
+    return -1</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H39" s="2">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2">
+        <v>1</v>
+      </c>
+      <c r="J39" s="2">
+        <v>1</v>
+      </c>
+      <c r="K39" s="2">
+        <v>1</v>
+      </c>
+      <c r="L39" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M39" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="N39" s="15">
+        <v>3</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="N39" s="2">
         <v>37.487000000000002</v>
       </c>
-      <c r="O39" s="15">
+      <c r="O39" s="2">
         <v>33.021999999999998</v>
       </c>
-      <c r="P39" s="15">
+      <c r="P39" s="2">
         <v>1024</v>
       </c>
-      <c r="Q39" s="15">
+      <c r="Q39" s="2">
         <f t="shared" si="1"/>
         <v>31.01</v>
       </c>
-      <c r="R39" s="15">
+      <c r="R39" s="2">
         <v>4.54</v>
       </c>
-      <c r="S39" s="15" t="s">
+      <c r="S39" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T39" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T39" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="U39" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="V39" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U39" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="V39" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" ht="19.95" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F40" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="G40" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15" t="str">
+        <v>63</v>
+      </c>
+      <c r="F40" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D15</f>
+        <v>Identify the bug in the following binary search implementation and explain how to fix it:
+def binary_search(arr, target):
+    low = 0
+    high = len(arr)
+    while low &lt; high:
+        mid = (low + high) // 2
+        if arr[mid] == target:
+            return mid
+        elif arr[mid] &lt; target:
+            low = mid
+        else:
+            high = mid - 1
+    return -1</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="H40" s="2">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2">
+        <v>1</v>
+      </c>
+      <c r="J40" s="2">
+        <v>1</v>
+      </c>
+      <c r="K40" s="2">
+        <v>1</v>
+      </c>
+      <c r="L40" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M40" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="N40" s="15">
+        <v>3</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="N40" s="2">
         <v>39.133000000000003</v>
       </c>
-      <c r="O40" s="15">
+      <c r="O40" s="2">
         <v>34.57</v>
       </c>
-      <c r="P40" s="15">
+      <c r="P40" s="2">
         <v>1024</v>
       </c>
-      <c r="Q40" s="15">
+      <c r="Q40" s="2">
         <f t="shared" si="1"/>
         <v>29.62</v>
       </c>
-      <c r="R40" s="15">
+      <c r="R40" s="2">
         <v>5.35</v>
       </c>
-      <c r="S40" s="15" t="s">
+      <c r="S40" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T40" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T40" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="U40" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="V40" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U40" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="V40" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" ht="19.95" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F41" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="G41" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="H41" s="15"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="15" t="str">
+        <v>63</v>
+      </c>
+      <c r="F41" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D16</f>
+        <v>Describe Floyd's Cycle-Finding Algorithm (Tortoise and Hare) for detecting a loop in a singly linked list. Explain why the time complexity is O(N) and the auxiliary space complexity is O(1).</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="H41" s="2">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2">
+        <v>1</v>
+      </c>
+      <c r="J41" s="2">
+        <v>1</v>
+      </c>
+      <c r="K41" s="2">
+        <v>1</v>
+      </c>
+      <c r="L41" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M41" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="N41" s="15">
+        <v>3</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="N41" s="2">
         <v>34.853000000000002</v>
       </c>
-      <c r="O41" s="15">
+      <c r="O41" s="2">
         <v>28.274999999999999</v>
       </c>
-      <c r="P41" s="15">
+      <c r="P41" s="2">
         <v>1024</v>
       </c>
-      <c r="Q41" s="15">
+      <c r="Q41" s="2">
         <f t="shared" si="1"/>
         <v>36.22</v>
       </c>
-      <c r="R41" s="15">
+      <c r="R41" s="2">
         <v>3.64</v>
       </c>
-      <c r="S41" s="15" t="s">
+      <c r="S41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T41" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T41" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="U41" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="V41" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="42" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U41" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" ht="19.95" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F42" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="G42" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15" t="str">
+        <v>63</v>
+      </c>
+      <c r="F42" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D16</f>
+        <v>Describe Floyd's Cycle-Finding Algorithm (Tortoise and Hare) for detecting a loop in a singly linked list. Explain why the time complexity is O(N) and the auxiliary space complexity is O(1).</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="H42" s="2">
+        <v>2</v>
+      </c>
+      <c r="I42" s="2">
+        <v>2</v>
+      </c>
+      <c r="J42" s="2">
+        <v>2</v>
+      </c>
+      <c r="K42" s="2">
+        <v>2</v>
+      </c>
+      <c r="L42" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M42" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="N42" s="15">
+        <v>8</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="N42" s="2">
         <v>37.076000000000001</v>
       </c>
-      <c r="O42" s="15">
+      <c r="O42" s="2">
         <v>32.579000000000001</v>
       </c>
-      <c r="P42" s="15">
+      <c r="P42" s="2">
         <v>1024</v>
       </c>
-      <c r="Q42" s="15">
+      <c r="Q42" s="2">
         <f t="shared" si="1"/>
         <v>31.43</v>
       </c>
-      <c r="R42" s="15">
+      <c r="R42" s="2">
         <v>4.53</v>
       </c>
-      <c r="S42" s="15" t="s">
+      <c r="S42" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T42" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T42" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="U42" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="V42" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U42" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="V42" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" ht="19.95" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F43" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="G43" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="15" t="str">
+        <v>63</v>
+      </c>
+      <c r="F43" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D16</f>
+        <v>Describe Floyd's Cycle-Finding Algorithm (Tortoise and Hare) for detecting a loop in a singly linked list. Explain why the time complexity is O(N) and the auxiliary space complexity is O(1).</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H43" s="2">
+        <v>0</v>
+      </c>
+      <c r="I43" s="2">
+        <v>1</v>
+      </c>
+      <c r="J43" s="2">
+        <v>1</v>
+      </c>
+      <c r="K43" s="2">
+        <v>1</v>
+      </c>
+      <c r="L43" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M43" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="N43" s="15">
+        <v>3</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="N43" s="2">
         <v>43.511000000000003</v>
       </c>
-      <c r="O43" s="15">
+      <c r="O43" s="2">
         <v>34.814</v>
       </c>
-      <c r="P43" s="15">
+      <c r="P43" s="2">
         <v>1024</v>
       </c>
-      <c r="Q43" s="15">
+      <c r="Q43" s="2">
         <f t="shared" si="1"/>
         <v>29.41</v>
       </c>
-      <c r="R43" s="15">
+      <c r="R43" s="2">
         <v>5.35</v>
       </c>
-      <c r="S43" s="15" t="s">
+      <c r="S43" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T43" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T43" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="U43" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="V43" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U43" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" ht="19.95" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F44" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="G44" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="H44" s="15"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="15"/>
-      <c r="K44" s="15"/>
-      <c r="L44" s="15" t="str">
+        <v>96</v>
+      </c>
+      <c r="F44" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D17</f>
+        <v>Propose an optimal algorithm in Python to find the Longest Increasing Subsequence (LIS) in O(N log N) time complexity using patience sorting / binary search. Provide the complete code, step-by-step invariant explanation, and complexity analysis.</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="H44" s="2">
+        <v>0</v>
+      </c>
+      <c r="I44" s="2">
+        <v>1</v>
+      </c>
+      <c r="J44" s="2">
+        <v>1</v>
+      </c>
+      <c r="K44" s="2">
+        <v>1</v>
+      </c>
+      <c r="L44" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M44" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="N44" s="15">
+        <v>3</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="N44" s="2">
         <v>32.491</v>
       </c>
-      <c r="O44" s="15">
+      <c r="O44" s="2">
         <v>28.245000000000001</v>
       </c>
-      <c r="P44" s="15">
+      <c r="P44" s="2">
         <v>1024</v>
       </c>
-      <c r="Q44" s="15">
+      <c r="Q44" s="2">
         <f t="shared" si="1"/>
         <v>36.25</v>
       </c>
-      <c r="R44" s="15">
+      <c r="R44" s="2">
         <v>3.64</v>
       </c>
-      <c r="S44" s="15" t="s">
+      <c r="S44" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T44" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T44" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="U44" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="V44" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="45" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U44" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" ht="19.95" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F45" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="G45" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15" t="str">
+        <v>96</v>
+      </c>
+      <c r="F45" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D17</f>
+        <v>Propose an optimal algorithm in Python to find the Longest Increasing Subsequence (LIS) in O(N log N) time complexity using patience sorting / binary search. Provide the complete code, step-by-step invariant explanation, and complexity analysis.</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="H45" s="2">
+        <v>0</v>
+      </c>
+      <c r="I45" s="2">
+        <v>1</v>
+      </c>
+      <c r="J45" s="2">
+        <v>1</v>
+      </c>
+      <c r="K45" s="2">
+        <v>1</v>
+      </c>
+      <c r="L45" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M45" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="N45" s="15">
+        <v>3</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="N45" s="2">
         <v>37.737000000000002</v>
       </c>
-      <c r="O45" s="15">
+      <c r="O45" s="2">
         <v>33.249000000000002</v>
       </c>
-      <c r="P45" s="15">
+      <c r="P45" s="2">
         <v>1024</v>
       </c>
-      <c r="Q45" s="15">
+      <c r="Q45" s="2">
         <f t="shared" si="1"/>
         <v>30.8</v>
       </c>
-      <c r="R45" s="15">
+      <c r="R45" s="2">
         <v>4.53</v>
       </c>
-      <c r="S45" s="15" t="s">
+      <c r="S45" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T45" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T45" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="U45" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="V45" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="46" spans="1:22" ht="39.6" customHeight="1">
+      <c r="U45" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" ht="19.95" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F46" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="G46" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15" t="str">
+        <v>96</v>
+      </c>
+      <c r="F46" s="3" t="str">
+        <f>'Question Bank &amp; Key'!D17</f>
+        <v>Propose an optimal algorithm in Python to find the Longest Increasing Subsequence (LIS) in O(N log N) time complexity using patience sorting / binary search. Provide the complete code, step-by-step invariant explanation, and complexity analysis.</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="H46" s="2">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2">
+        <v>1</v>
+      </c>
+      <c r="J46" s="2">
+        <v>1</v>
+      </c>
+      <c r="K46" s="2">
+        <v>1</v>
+      </c>
+      <c r="L46" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M46" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="N46" s="15">
+        <v>3</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="N46" s="2">
         <v>43.338999999999999</v>
       </c>
-      <c r="O46" s="15">
+      <c r="O46" s="2">
         <v>35.213000000000001</v>
       </c>
-      <c r="P46" s="15">
+      <c r="P46" s="2">
         <v>1024</v>
       </c>
-      <c r="Q46" s="15">
+      <c r="Q46" s="2">
         <f t="shared" si="1"/>
         <v>29.08</v>
       </c>
-      <c r="R46" s="15">
+      <c r="R46" s="2">
         <v>5.35</v>
       </c>
-      <c r="S46" s="15" t="s">
+      <c r="S46" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T46" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T46" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="U46" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="V46" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="51" spans="4:21">
-      <c r="D51" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
-      <c r="I51" s="19"/>
-      <c r="J51" s="19"/>
-      <c r="K51" s="19"/>
-      <c r="L51" s="19"/>
-      <c r="M51" s="19"/>
-      <c r="N51" s="19"/>
-      <c r="O51" s="19"/>
-      <c r="P51" s="19"/>
-      <c r="Q51" s="19"/>
-      <c r="R51" s="19"/>
-      <c r="S51" s="19"/>
-      <c r="T51" s="19"/>
-      <c r="U51" s="19"/>
-    </row>
-    <row r="52" spans="4:21">
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="19"/>
-      <c r="J52" s="19"/>
-      <c r="K52" s="19"/>
-      <c r="L52" s="19"/>
-      <c r="M52" s="19"/>
-      <c r="N52" s="19"/>
-      <c r="O52" s="19"/>
-      <c r="P52" s="19"/>
-      <c r="Q52" s="19"/>
-      <c r="R52" s="19"/>
-      <c r="S52" s="19"/>
-      <c r="T52" s="19"/>
-      <c r="U52" s="19"/>
-    </row>
-    <row r="53" spans="4:21">
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="19"/>
-      <c r="J53" s="19"/>
-      <c r="K53" s="19"/>
-      <c r="L53" s="19"/>
-      <c r="M53" s="19"/>
-      <c r="N53" s="19"/>
-      <c r="O53" s="19"/>
-      <c r="P53" s="19"/>
-      <c r="Q53" s="19"/>
-      <c r="R53" s="19"/>
-      <c r="S53" s="19"/>
-      <c r="T53" s="19"/>
-      <c r="U53" s="19"/>
+      <c r="U46" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>272</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="D51:U53"/>
-  </mergeCells>
   <dataValidations count="3">
     <dataValidation type="whole" allowBlank="1" errorTitle="Invalid Score Range" error="Enter 0, 1, or 2 as per the rubric." promptTitle="Rubric Score" prompt="Score: 0, 1, or 2" sqref="H2:K46" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>0</formula1>
@@ -5428,7 +6030,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>
 
@@ -5444,7 +6045,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="25.95" customHeight="1">
@@ -5452,16 +6053,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="22.05" customHeight="1">
@@ -5470,11 +6071,11 @@
       </c>
       <c r="B4" s="6">
         <f>ROUND(COUNTIFS('Scoring Register'!$C$2:$C$46, "phi4-mini-reasoning", 'Scoring Register'!$H$2:$H$46, 2) / 15 * 100, 1)</f>
-        <v>0</v>
-      </c>
-      <c r="C4" s="6" t="str">
+        <v>40</v>
+      </c>
+      <c r="C4" s="6">
         <f>IFERROR(ROUND(AVERAGEIF('Scoring Register'!$C$2:$C$46, "phi4-mini-reasoning", 'Scoring Register'!$L$2:$L$46), 2), "-")</f>
-        <v>-</v>
+        <v>5</v>
       </c>
       <c r="D4" s="6">
         <f>IFERROR(ROUND(AVERAGEIF('Scoring Register'!$C$2:$C$46, "phi4-mini-reasoning", 'Scoring Register'!$N$2:$N$46), 2), "-")</f>
@@ -5491,11 +6092,11 @@
       </c>
       <c r="B5" s="6">
         <f>ROUND(COUNTIFS('Scoring Register'!$C$2:$C$46, "deepseek-r1:7b", 'Scoring Register'!$H$2:$H$46, 2) / 15 * 100, 1)</f>
-        <v>0</v>
-      </c>
-      <c r="C5" s="6" t="str">
+        <v>53.3</v>
+      </c>
+      <c r="C5" s="6">
         <f>IFERROR(ROUND(AVERAGEIF('Scoring Register'!$C$2:$C$46, "deepseek-r1:7b", 'Scoring Register'!$L$2:$L$46), 2), "-")</f>
-        <v>-</v>
+        <v>5.67</v>
       </c>
       <c r="D5" s="6">
         <f>IFERROR(ROUND(AVERAGEIF('Scoring Register'!$C$2:$C$46, "deepseek-r1:7b", 'Scoring Register'!$N$2:$N$46), 2), "-")</f>
@@ -5508,15 +6109,15 @@
     </row>
     <row r="6" spans="1:5" ht="22.05" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="6">
         <f>ROUND(COUNTIFS('Scoring Register'!$C$2:$C$46, "qwen3:8b", 'Scoring Register'!$H$2:$H$46, 2) / 15 * 100, 1)</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="6" t="str">
+        <v>26.7</v>
+      </c>
+      <c r="C6" s="6">
         <f>IFERROR(ROUND(AVERAGEIF('Scoring Register'!$C$2:$C$46, "qwen3:8b", 'Scoring Register'!$L$2:$L$46), 2), "-")</f>
-        <v>-</v>
+        <v>4.33</v>
       </c>
       <c r="D6" s="6">
         <f>IFERROR(ROUND(AVERAGEIF('Scoring Register'!$C$2:$C$46, "qwen3:8b", 'Scoring Register'!$N$2:$N$46), 2), "-")</f>
@@ -5544,77 +6145,77 @@
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>249</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>250</v>
+        <v>279</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>251</v>
+        <v>280</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>253</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="24" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>254</v>
+        <v>283</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>256</v>
+        <v>285</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>257</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="24" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>258</v>
+        <v>287</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>261</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="24" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="24" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -5630,14 +6231,14 @@
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>270</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="28.05" customHeight="1">
@@ -5651,254 +6252,314 @@
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>273</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="48" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
+      <c r="D3" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="48" customHeight="1">
-      <c r="A4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="12" t="s">
+      <c r="A4" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+      <c r="D4" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="48" customHeight="1">
-      <c r="A5" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="12" t="s">
+      <c r="A5" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
+      <c r="C5" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="48" customHeight="1">
-      <c r="A6" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
+      <c r="C6" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="79.95" customHeight="1">
-      <c r="A7" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="12" t="s">
+      <c r="A7" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="C7" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="64.05" customHeight="1">
-      <c r="A8" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="11" t="s">
+      <c r="A8" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
+      <c r="D8" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="64.05" customHeight="1">
-      <c r="A9" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" s="11" t="s">
+      <c r="A9" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="D9" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="79.95" customHeight="1">
-      <c r="A10" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
+      <c r="A10" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="79.95" customHeight="1">
-      <c r="A11" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="A11" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="12" spans="1:6" ht="96" customHeight="1">
-      <c r="A12" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="A12" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="13" spans="1:6" ht="79.95" customHeight="1">
-      <c r="A13" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="C13" s="11" t="s">
+      <c r="A13" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="D13" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="14" spans="1:6" ht="127.95" customHeight="1">
-      <c r="A14" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="C14" s="11" t="s">
+      <c r="A14" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
+      <c r="D14" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="15" spans="1:6" ht="223.95" customHeight="1">
-      <c r="A15" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="A15" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="16" spans="1:6" ht="79.95" customHeight="1">
-      <c r="A16" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
+      <c r="A16" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="17" spans="1:6" ht="96" customHeight="1">
-      <c r="A17" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
+      <c r="A17" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>347</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
